--- a/DarkJargon_SoK_taxonomy_tables.xlsx
+++ b/DarkJargon_SoK_taxonomy_tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Projekte\DarkJargon-SOK-USENIX26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36A761A5-BDB8-46BF-9D33-896CACE450CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABDCB65F-9197-4D48-81C4-2DA6E3C44108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21360" firstSheet="1" activeTab="1" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="3" activeTab="5" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -27,8 +27,6 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId11"/>
-    <pivotCache cacheId="1" r:id="rId12"/>
-    <pivotCache cacheId="2" r:id="rId13"/>
   </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
@@ -48,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="973" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="524">
   <si>
     <t>Approaches</t>
   </si>
@@ -509,22 +507,7 @@
     <t>IEEE Xplore</t>
   </si>
   <si>
-    <t>kaggle</t>
-  </si>
-  <si>
-    <t>scholar  - mdpi</t>
-  </si>
-  <si>
-    <t>scholar - University of cambridge repository</t>
-  </si>
-  <si>
-    <t>scholar - usenix</t>
-  </si>
-  <si>
     <t>sciencedirect</t>
-  </si>
-  <si>
-    <t>(blank)</t>
   </si>
   <si>
     <t>Springer</t>
@@ -1111,9 +1094,6 @@
   </si>
   <si>
     <t>1000 detected sample keywords</t>
-  </si>
-  <si>
-    <t>46 DEA terms (for autmatic labeling), raw data labelled</t>
   </si>
   <si>
     <t>masked known entities in  sentences</t>
@@ -2617,6 +2597,9 @@
   </si>
   <si>
     <t>yuan2018</t>
+  </si>
+  <si>
+    <t>46 DEA terms (for automatic labeling), raw data labelled</t>
   </si>
 </sst>
 </file>
@@ -3032,14 +3015,14 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3202,9 +3185,6 @@
                 <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="5">
                   <c:v>3</c:v>
                 </c:pt>
@@ -3356,7 +3336,10 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -3444,6 +3427,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -3739,6 +3723,10 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3967,7 +3955,7 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4098,7 +4086,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4149,7 +4137,19 @@
           </c:marker>
           <c:dLbls>
             <c:dLbl>
-              <c:idx val="6"/>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:r>
+                      <a:rPr lang="en-US"/>
+                      <a:t>4</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
               <c:dLblPos val="t"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
@@ -4159,26 +4159,11 @@
               <c:showBubbleSize val="0"/>
               <c:separator>, </c:separator>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000001-2B7D-45CB-B640-4D6FAA284A90}"/>
-                </c:ext>
-              </c:extLst>
-            </c:dLbl>
-            <c:dLbl>
-              <c:idx val="7"/>
-              <c:dLblPos val="t"/>
-              <c:showLegendKey val="0"/>
-              <c:showVal val="1"/>
-              <c:showCatName val="0"/>
-              <c:showSerName val="0"/>
-              <c:showPercent val="0"/>
-              <c:showBubbleSize val="0"/>
-              <c:separator>, </c:separator>
-              <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                  <c16:uniqueId val="{00000000-2B7D-45CB-B640-4D6FAA284A90}"/>
+                  <c16:uniqueId val="{00000000-3492-46B7-88A8-AB8D1C4D3A6B}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -4214,6 +4199,7 @@
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -4229,7 +4215,7 @@
                     <a:avLst/>
                   </a:prstGeom>
                 </c15:spPr>
-                <c15:showLeaderLines val="1"/>
+                <c15:showLeaderLines val="0"/>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -4284,7 +4270,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>6</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>3</c:v>
@@ -4368,7 +4354,7 @@
                     <a:uFillTx/>
                     <a:latin typeface="Aptos Narrow"/>
                   </a:rPr>
-                  <a:t>Number of papers</a:t>
+                  <a:t>number of papers</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -4428,11 +4414,19 @@
                     <a:uFillTx/>
                     <a:latin typeface="Aptos Narrow"/>
                   </a:rPr>
-                  <a:t>Databases</a:t>
+                  <a:t>databases</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.43436766396401871"/>
+              <c:y val="0.80820188785900682"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -4496,6 +4490,10 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="t"/>
+      <c:legendEntry>
+        <c:idx val="2"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -4579,768 +4577,6 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <c:style val="2"/>
-  <c:chart>
-    <c:autoTitleDeleted val="1"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="stacked"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>years_dist!$B$19:$B$19</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>approach</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="0D94C7"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:tabLst/>
-                  <a:defRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="404040"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:separator>, </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <a:prstGeom prst="rect">
-                    <a:avLst/>
-                  </a:prstGeom>
-                </c15:spPr>
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>years_dist!$A$20:$A$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>years_dist!$B$20:$B$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-72BA-4097-839B-63693F525107}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>years_dist!$C$19:$C$19</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>resource</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="6AB0DC"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:tabLst/>
-                  <a:defRPr lang="en-US" sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="404040"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:separator>, </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <a:prstGeom prst="rect">
-                    <a:avLst/>
-                  </a:prstGeom>
-                </c15:spPr>
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>years_dist!$A$20:$A$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>years_dist!$C$20:$C$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-72BA-4097-839B-63693F525107}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:overlap val="100"/>
-        <c:axId val="727843631"/>
-        <c:axId val="727842671"/>
-      </c:barChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>years_dist!$D$19:$D$19</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Grand Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:tabLst/>
-                  <a:defRPr lang="en-US" sz="800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="404040"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:separator>, </c:separator>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-                  <a:prstGeom prst="rect">
-                    <a:avLst/>
-                  </a:prstGeom>
-                </c15:spPr>
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>years_dist!$A$20:$A$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>years_dist!$D$20:$D$29</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-72BA-4097-839B-63693F525107}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="727843631"/>
-        <c:axId val="727842671"/>
-      </c:lineChart>
-      <c:valAx>
-        <c:axId val="727842671"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9528" cap="flat">
-              <a:solidFill>
-                <a:srgbClr val="D9D9D9"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:tabLst/>
-                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="595959"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="595959"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:rPr>
-                  <a:t>Number of papers</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="727843631"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:catAx>
-        <c:axId val="727843631"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr marL="0" marR="0" indent="0" algn="ctr" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-                  <a:lnSpc>
-                    <a:spcPct val="100000"/>
-                  </a:lnSpc>
-                  <a:spcBef>
-                    <a:spcPts val="0"/>
-                  </a:spcBef>
-                  <a:spcAft>
-                    <a:spcPts val="0"/>
-                  </a:spcAft>
-                  <a:tabLst/>
-                  <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="595959"/>
-                    </a:solidFill>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="595959"/>
-                    </a:solidFill>
-                    <a:uFillTx/>
-                    <a:latin typeface="Aptos Narrow"/>
-                  </a:rPr>
-                  <a:t>Years</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9528" cap="flat">
-            <a:solidFill>
-              <a:srgbClr val="D9D9D9"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr marL="0" marR="0" indent="0" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-              <a:lnSpc>
-                <a:spcPct val="100000"/>
-              </a:lnSpc>
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:tabLst/>
-              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="595959"/>
-                </a:solidFill>
-                <a:latin typeface="Aptos Narrow"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="727842671"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr marL="0" marR="0" indent="0" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-            <a:lnSpc>
-              <a:spcPct val="100000"/>
-            </a:lnSpc>
-            <a:spcBef>
-              <a:spcPts val="0"/>
-            </a:spcBef>
-            <a:spcAft>
-              <a:spcPts val="0"/>
-            </a:spcAft>
-            <a:tabLst/>
-            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="595959"/>
-              </a:solidFill>
-              <a:latin typeface="Aptos Narrow"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln w="9528" cap="flat">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr lIns="0" tIns="0" rIns="0" bIns="0"/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr marL="0" marR="0" indent="0" defTabSz="914400" fontAlgn="auto" hangingPunct="1">
-        <a:lnSpc>
-          <a:spcPct val="100000"/>
-        </a:lnSpc>
-        <a:spcBef>
-          <a:spcPts val="0"/>
-        </a:spcBef>
-        <a:spcAft>
-          <a:spcPts val="0"/>
-        </a:spcAft>
-        <a:tabLst/>
-        <a:defRPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:latin typeface="Aptos Narrow"/>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6718,7 +5954,7 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>15243</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3421383" cy="1992633"/>
+    <xdr:ext cx="3421383" cy="1691637"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 5">
@@ -6751,10 +5987,10 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>232229</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>153484</xdr:rowOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>120354</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="3242129" cy="2275118"/>
+    <xdr:ext cx="3242129" cy="2066256"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -6773,37 +6009,6 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>219887</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>108313</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="3535685" cy="1905544"/>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A95B39F-C655-C5F3-6800-A06BCFE78C78}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7808,81 +7013,6 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="" refreshedDate="0" createdVersion="8" refreshedVersion="8" recordCount="0" xr:uid="{BADFD105-F23A-4FDB-B3AB-389A44F149FA}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A9" sheet="publication"/>
-  </cacheSource>
-  <cacheFields count="13">
-    <cacheField name="type simp" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="library" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="title" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="conference" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="journal" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="preprint" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="not academic" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="name of pub" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="year" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="year-month" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="peer reviewd" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="type" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="focused on" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="" refreshedDate="0" createdVersion="8" refreshedVersion="8" recordCount="0" xr:uid="{05BA9BDA-00F9-43BE-BF45-9CFD1041B86E}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A2:B17" sheet="terms"/>
-  </cacheSource>
-  <cacheFields count="2">
-    <cacheField name="jargon" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="A Novel Framework of Identifying Chinese Jargons for Telegram Underground Markets" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9E0E3A19-2E91-465C-B843-2F7B3E67EE98}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0">
   <location ref="A3:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
@@ -7961,124 +7091,6 @@
   </colFields>
   <dataFields count="1">
     <dataField name="Count of type simp" fld="0" subtotal="count" baseField="0" baseItem="1048828"/>
-  </dataFields>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{15663DA3-8DC9-4EA0-8327-0C4E8C2D7C06}" name="PivotTable10" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0">
-  <location ref="A3:D16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField axis="axisCol" dataField="1" compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <dataFields count="1">
-    <dataField name="Count of type simp" fld="0" subtotal="count" baseField="0" baseItem="1048828"/>
-  </dataFields>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{69A91DE7-C09A-461C-B8B5-B4EA648E156C}" name="PivotTable11" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0">
-  <location ref="A3:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField axis="axisRow" dataField="1" compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <dataFields count="1">
-    <dataField name="Count of jargon" fld="0" subtotal="count" baseField="0" baseItem="1048828"/>
   </dataFields>
   <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -8875,7 +7887,7 @@
     </row>
     <row r="17" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -8902,7 +7914,7 @@
     </row>
     <row r="18" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -8944,85 +7956,85 @@
   <sheetData>
     <row r="1" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="H1" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="54" t="s">
-        <v>399</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
+      <c r="A2" s="55" t="s">
+        <v>393</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
     </row>
     <row r="3" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="C3" s="1">
         <v>2022</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -9030,31 +8042,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C4" s="1">
         <v>2017</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -9062,34 +8074,34 @@
         <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C5" s="1">
         <v>2019</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K5" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -9097,66 +8109,66 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C6" s="1">
         <v>2017</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="C7" s="1">
         <v>2015</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="K7" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -9164,28 +8176,28 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C8" s="1">
         <v>2007</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="E8" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K8" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -9197,338 +8209,338 @@
         <v>2018</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="K9" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="55" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55" t="s">
-        <v>411</v>
+        <v>404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="56" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="56" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1">
         <v>2021</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>2018</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E12" s="32" t="s">
+        <v>408</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G12" t="s">
+        <v>160</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="E12" s="32" t="s">
-        <v>414</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="G12" t="s">
-        <v>165</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="K12" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="54" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54" t="s">
-        <v>417</v>
+        <v>410</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="55" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="55" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C14" s="1">
         <v>2023</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E14" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C15" s="1">
         <v>2016</v>
       </c>
       <c r="D15" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E15" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="F15" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="G15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="J15" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="C16" s="1">
         <v>2022</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C17" s="1">
         <v>2024</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="1">
         <v>2018</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E18" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="C19" s="1">
         <v>2024</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E19" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C20" s="1">
         <v>2017</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="C21" s="1">
         <v>2024</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -9565,25 +8577,25 @@
     <row r="1" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="J1" s="7" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>32</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>33</v>
@@ -9610,25 +8622,25 @@
     <row r="2" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="J2" s="11" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N2" s="11" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>100</v>
@@ -9649,29 +8661,29 @@
         <v>46</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="J3" s="11" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>66</v>
@@ -9692,7 +8704,7 @@
         <v>46</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -9701,25 +8713,25 @@
     <row r="4" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="J4" s="11" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="N4" s="11" t="s">
         <v>117</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>49</v>
@@ -9740,7 +8752,7 @@
         <v>46</v>
       </c>
       <c r="W4" s="36" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -9749,25 +8761,25 @@
     <row r="5" spans="1:26" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="J5" s="11" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>93</v>
@@ -9788,7 +8800,7 @@
         <v>46</v>
       </c>
       <c r="W5" s="36" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -9797,25 +8809,25 @@
     <row r="6" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="J6" s="11" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L6" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="O6" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="M6" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="N6" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="O6" s="11" t="s">
-        <v>508</v>
-      </c>
       <c r="P6" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q6" s="11" t="s">
         <v>118</v>
@@ -9836,7 +8848,7 @@
         <v>46</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -9845,25 +8857,25 @@
     <row r="7" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="J7" s="11" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L7" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="O7" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="M7" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="O7" s="11" t="s">
-        <v>508</v>
-      </c>
       <c r="P7" s="11" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="Q7" s="11" t="s">
         <v>41</v>
@@ -9884,34 +8896,34 @@
         <v>46</v>
       </c>
       <c r="W7" s="35" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="J8" s="11" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="N8" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>112</v>
@@ -9932,7 +8944,7 @@
         <v>77</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -9941,25 +8953,25 @@
     <row r="9" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="J9" s="11" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>99</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q9" s="11" t="s">
         <v>72</v>
@@ -9980,7 +8992,7 @@
         <v>77</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
@@ -9989,25 +9001,25 @@
     <row r="10" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="J10" s="11" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="K10" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>499</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="N10" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="L10" s="11" t="s">
-        <v>505</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="N10" s="37" t="s">
-        <v>233</v>
-      </c>
       <c r="O10" s="37" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="P10" s="37" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="Q10" s="37"/>
       <c r="R10" s="37"/>
@@ -10020,28 +9032,28 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="J11" s="11" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>79</v>
@@ -10070,25 +9082,25 @@
     </row>
     <row r="12" spans="1:26" ht="331.2" x14ac:dyDescent="0.3">
       <c r="J12" s="11" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="Q12" s="11" t="s">
         <v>106</v>
@@ -10109,7 +9121,7 @@
         <v>46</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -10119,25 +9131,25 @@
       <c r="A13" s="6"/>
       <c r="I13" s="10"/>
       <c r="J13" s="11" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="Q13" s="11" t="s">
         <v>128</v>
@@ -10164,25 +9176,25 @@
     <row r="14" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="J14" s="11" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="Q14" s="11" t="s">
         <v>54</v>
@@ -10203,7 +9215,7 @@
         <v>46</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -10212,25 +9224,25 @@
     <row r="15" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="J15" s="11" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Q15" s="11" t="s">
         <v>60</v>
@@ -10251,7 +9263,7 @@
         <v>46</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -10260,31 +9272,31 @@
     <row r="16" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="J16" s="11" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="K16" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="L16" s="37" t="s">
+        <v>494</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="N16" s="37" t="s">
         <v>228</v>
       </c>
-      <c r="L16" s="37" t="s">
-        <v>500</v>
-      </c>
-      <c r="M16" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="N16" s="37" t="s">
-        <v>233</v>
-      </c>
       <c r="O16" s="37" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="P16" s="37" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="Q16" s="37" t="s">
         <v>123</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="S16" s="37" t="s">
         <v>124</v>
@@ -10299,34 +9311,34 @@
         <v>77</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="216" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="J17" s="11" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>86</v>
@@ -10347,7 +9359,7 @@
         <v>91</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -10740,40 +9752,40 @@
         <v>139</v>
       </c>
       <c r="B1" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C1" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D1" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="F1" t="s">
         <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="193.8" x14ac:dyDescent="0.3">
@@ -10781,10 +9793,10 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="E3" s="31" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -10793,10 +9805,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -10805,119 +9817,119 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="1" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B6" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E6" s="1">
         <v>0.6</v>
       </c>
       <c r="F6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="B7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F7" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B8" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="C8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="F8" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="B9" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="E11" s="1">
         <v>0.31</v>
       </c>
       <c r="F11" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B12" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C12" s="30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E12" s="1">
         <v>0.60560000000000003</v>
@@ -10925,189 +9937,189 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B13" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C13" s="30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E13" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F13" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="C14" s="30"/>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="B15" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="F15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B16" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="C16" s="30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E16" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F16" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="C17" s="30"/>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B18" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C18" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="F18" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B19" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C19" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F19" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C20" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="D21" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C22" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F22" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G22" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B23" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C23" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="E23" s="1">
         <v>94.3</v>
       </c>
       <c r="F23" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B24" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="C24" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F24" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -11375,7 +10387,7 @@
         <v>1</v>
       </c>
       <c r="C23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -11385,7 +10397,7 @@
       <c r="A24">
         <v>2019</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>1</v>
       </c>
       <c r="D24">
@@ -11458,10 +10470,10 @@
         <v>136</v>
       </c>
       <c r="B30">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C30">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D30">
         <v>27</v>
@@ -11476,7 +10488,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F8EC5-B561-4123-A5F6-54D916B5F663}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A3:D27"/>
+  <dimension ref="A19:D27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.88671875" bestFit="1" customWidth="1"/>
@@ -11486,182 +10498,6 @@
     <col min="5" max="5" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="B5" s="14">
-        <v>1</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="B6" s="18">
-        <v>1</v>
-      </c>
-      <c r="C6" s="19">
-        <v>3</v>
-      </c>
-      <c r="D6" s="26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="B7" s="18">
-        <v>5</v>
-      </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="18">
-        <v>1</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B9" s="18">
-        <v>5</v>
-      </c>
-      <c r="C9" s="19">
-        <v>1</v>
-      </c>
-      <c r="D9" s="26">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="19">
-        <v>1</v>
-      </c>
-      <c r="D10" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="B11" s="18">
-        <v>1</v>
-      </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B12" s="18">
-        <v>1</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="18">
-        <v>1</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="18">
-        <v>2</v>
-      </c>
-      <c r="C14" s="19">
-        <v>1</v>
-      </c>
-      <c r="D14" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="19">
-        <v>3</v>
-      </c>
-      <c r="D15" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="21">
-        <v>18</v>
-      </c>
-      <c r="C16" s="22">
-        <v>9</v>
-      </c>
-      <c r="D16" s="13">
-        <v>27</v>
-      </c>
-    </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>139</v>
@@ -11675,7 +10511,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -11728,12 +10564,12 @@
         <v>4</v>
       </c>
       <c r="D24">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -11744,10 +10580,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -11758,10 +10594,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -11769,14 +10605,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA0438A-EE17-4255-B1AE-346A842E6C2A}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A3:B22"/>
+  <dimension ref="A15:B22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -11784,84 +10620,12 @@
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B4" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B11" s="13">
-        <v>16</v>
-      </c>
-    </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>135</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -11874,7 +10638,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="17" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B17" s="26">
         <v>1</v>
@@ -11890,7 +10654,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="17" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="B19" s="26">
         <v>1</v>
@@ -11922,7 +10686,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11938,29 +10702,29 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B1" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="C1" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>75</v>
@@ -11968,18 +10732,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -11987,7 +10751,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>75</v>
@@ -11995,29 +10759,29 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>44</v>
@@ -12025,10 +10789,10 @@
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
@@ -12036,7 +10800,7 @@
     </row>
     <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>75</v>
@@ -12047,40 +10811,40 @@
     </row>
     <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>44</v>
@@ -12091,21 +10855,21 @@
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
@@ -12134,43 +10898,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>160</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -12178,12 +10942,12 @@
         <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G2" s="1">
         <v>2025</v>
@@ -12192,16 +10956,16 @@
         <v>45870</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>141</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>139</v>
@@ -12212,12 +10976,12 @@
         <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G3" s="1">
         <v>2023</v>
@@ -12226,16 +10990,16 @@
         <v>45108</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>139</v>
@@ -12246,12 +11010,12 @@
         <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G4" s="1">
         <v>2022</v>
@@ -12260,16 +11024,16 @@
         <v>44593</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>143</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>139</v>
@@ -12280,12 +11044,12 @@
         <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="F5" s="28" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G5" s="28">
         <v>2025</v>
@@ -12294,16 +11058,16 @@
         <v>45839</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>143</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>139</v>
@@ -12314,12 +11078,12 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G6" s="1">
         <v>2024</v>
@@ -12328,16 +11092,16 @@
         <v>45413</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>143</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>139</v>
@@ -12348,12 +11112,12 @@
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="F7" s="28" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G7" s="28">
         <v>2021</v>
@@ -12362,16 +11126,16 @@
         <v>44197</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>143</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>139</v>
@@ -12384,10 +11148,10 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G8" s="1">
         <v>2024</v>
@@ -12400,10 +11164,10 @@
         <v>144</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>139</v>
@@ -12414,12 +11178,12 @@
         <v>111</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G9" s="1">
         <v>2016</v>
@@ -12428,16 +11192,16 @@
         <v>42614</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>145</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>139</v>
@@ -12448,12 +11212,12 @@
         <v>116</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G10" s="1">
         <v>2021</v>
@@ -12462,16 +11226,16 @@
         <v>44317</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>145</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>139</v>
@@ -12482,12 +11246,12 @@
         <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G11" s="1">
         <v>2023</v>
@@ -12496,16 +11260,16 @@
         <v>45139</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>145</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>139</v>
@@ -12516,12 +11280,12 @@
         <v>122</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G12" s="1">
         <v>2017</v>
@@ -12530,32 +11294,32 @@
         <v>42856</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>145</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="54" t="s">
         <v>127</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G13" s="1">
         <v>2024</v>
@@ -12564,16 +11328,16 @@
         <v>45383</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>139</v>
@@ -12584,12 +11348,12 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G14" s="1">
         <v>2023</v>
@@ -12598,16 +11362,16 @@
         <v>45108</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>139</v>
@@ -12618,12 +11382,12 @@
         <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G15" s="1">
         <v>2018</v>
@@ -12632,16 +11396,16 @@
         <v>43313</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>139</v>
@@ -12653,11 +11417,11 @@
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G16" s="1">
         <v>2024</v>
@@ -12666,16 +11430,16 @@
         <v>45413</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>139</v>
@@ -12683,13 +11447,13 @@
     </row>
     <row r="17" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="G17" s="1">
         <v>2021</v>
@@ -12698,16 +11462,16 @@
         <v>44378</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>143</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>139</v>
@@ -12718,10 +11482,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G18" s="1">
         <v>2017</v>
@@ -12730,16 +11494,16 @@
         <v>42826</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>140</v>
@@ -12750,10 +11514,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G19" s="1">
         <v>2019</v>
@@ -12762,16 +11526,16 @@
         <v>43617</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>139</v>
@@ -12782,10 +11546,10 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G20" s="1">
         <v>2017</v>
@@ -12794,16 +11558,16 @@
         <v>42979</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>140</v>
@@ -12814,10 +11578,10 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G21" s="1">
         <v>2022</v>
@@ -12826,16 +11590,16 @@
         <v>44743</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>140</v>
@@ -12843,10 +11607,10 @@
     </row>
     <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E22" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G22" s="1">
         <v>2015</v>
@@ -12855,10 +11619,10 @@
         <v>43101</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>140</v>
@@ -12869,7 +11633,7 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F23"/>
       <c r="G23" s="1">
@@ -12879,10 +11643,10 @@
         <v>2007</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>140</v>
@@ -12893,7 +11657,7 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G24" s="1">
         <v>2018</v>
@@ -12902,10 +11666,10 @@
         <v>43101</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L24" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>140</v>
@@ -13004,32 +11768,32 @@
         <v>29</v>
       </c>
       <c r="F1" s="38" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="G1" s="38" t="s">
         <v>31</v>
       </c>
       <c r="H1" s="38" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="I1" s="38" t="s">
         <v>32</v>
       </c>
       <c r="J1" s="38" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="K1" s="39" t="s">
         <v>38</v>
       </c>
       <c r="L1" s="40"/>
       <c r="M1" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="N1" s="38" t="s">
+        <v>320</v>
+      </c>
+      <c r="O1" s="41" t="s">
         <v>326</v>
-      </c>
-      <c r="N1" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="O1" s="41" t="s">
-        <v>331</v>
       </c>
       <c r="P1" s="41"/>
       <c r="Q1" s="40"/>
@@ -13039,35 +11803,35 @@
     </row>
     <row r="2" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
       <c r="E2" s="42" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="F2" s="42" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="G2" s="42" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="H2" s="42" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I2" s="42" t="s">
         <v>48</v>
       </c>
       <c r="J2" s="38" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="K2" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L2" s="40"/>
       <c r="M2" s="42" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="N2" s="43" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="O2" s="41" t="s">
-        <v>347</v>
+        <v>523</v>
       </c>
       <c r="P2" s="41"/>
       <c r="Q2" s="40"/>
@@ -13077,35 +11841,35 @@
     </row>
     <row r="3" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
       <c r="E3" s="42" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="F3" s="42" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="G3" s="42" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I3" s="42" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J3" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K3" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L3" s="40"/>
       <c r="M3" s="41" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="N3" s="41" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="O3" s="44" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="P3" s="41"/>
       <c r="Q3" s="40"/>
@@ -13115,35 +11879,35 @@
     </row>
     <row r="4" spans="5:20" ht="156.6" x14ac:dyDescent="0.3">
       <c r="E4" s="42" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G4" s="42" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H4" s="42" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="I4" s="42" t="s">
         <v>117</v>
       </c>
       <c r="J4" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K4" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L4" s="40"/>
       <c r="M4" s="45" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
       <c r="N4" s="41" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="O4" s="41" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="P4" s="41"/>
       <c r="Q4" s="40"/>
@@ -13153,33 +11917,33 @@
     </row>
     <row r="5" spans="5:20" ht="96.6" x14ac:dyDescent="0.3">
       <c r="E5" s="42" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G5" s="42" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H5" s="42" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I5" s="42" t="s">
         <v>85</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K5" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L5" s="40"/>
       <c r="M5" s="45" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="N5" s="41"/>
       <c r="O5" s="41" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="P5" s="41"/>
       <c r="Q5" s="40"/>
@@ -13189,35 +11953,35 @@
     </row>
     <row r="6" spans="5:20" ht="288" x14ac:dyDescent="0.3">
       <c r="E6" s="42" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G6" s="42" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H6" s="42" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I6" s="42" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K6" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L6" s="40"/>
       <c r="M6" s="46" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N6" s="41" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="O6" s="41" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="P6" s="41"/>
       <c r="Q6" s="40"/>
@@ -13227,35 +11991,35 @@
     </row>
     <row r="7" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
       <c r="E7" s="42" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G7" s="42" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H7" s="42" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="J7" s="42" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="K7" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L7" s="40"/>
       <c r="M7" s="41" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N7" s="41" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="O7" s="41" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="P7" s="41"/>
       <c r="Q7" s="40"/>
@@ -13265,35 +12029,35 @@
     </row>
     <row r="8" spans="5:20" ht="79.8" x14ac:dyDescent="0.3">
       <c r="E8" s="42" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G8" s="42" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="H8" s="42" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="I8" s="42" t="s">
         <v>85</v>
       </c>
       <c r="J8" s="38" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="K8" s="42" t="s">
         <v>77</v>
       </c>
       <c r="L8" s="40"/>
       <c r="M8" s="47" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="N8" s="47" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="O8" s="41" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="P8" s="41"/>
       <c r="Q8" s="40"/>
@@ -13303,35 +12067,35 @@
     </row>
     <row r="9" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="E9" s="42" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="F9" s="42" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="G9" s="42" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H9" s="42" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="I9" s="42" t="s">
         <v>99</v>
       </c>
       <c r="J9" s="42" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="K9" s="42" t="s">
         <v>77</v>
       </c>
       <c r="L9" s="40"/>
       <c r="M9" s="41" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="N9" s="48" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="O9" s="41" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="P9" s="41"/>
       <c r="Q9" s="40"/>
@@ -13341,22 +12105,22 @@
     </row>
     <row r="10" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="E10" s="49" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="F10" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="H10" s="42" t="s">
+        <v>240</v>
+      </c>
+      <c r="I10" s="49" t="s">
         <v>228</v>
       </c>
-      <c r="G10" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="H10" s="42" t="s">
-        <v>245</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>233</v>
-      </c>
       <c r="J10" s="49" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="K10" s="49" t="s">
         <v>46</v>
@@ -13365,7 +12129,7 @@
       <c r="M10" s="40"/>
       <c r="N10" s="50"/>
       <c r="O10" s="41" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="P10" s="41"/>
       <c r="Q10" s="40"/>
@@ -13375,35 +12139,35 @@
     </row>
     <row r="11" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
       <c r="E11" s="42" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G11" s="42" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H11" s="42" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="J11" s="42" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="K11" s="42" t="s">
         <v>77</v>
       </c>
       <c r="L11" s="40"/>
       <c r="M11" s="41" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="N11" s="48" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="O11" s="41" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="P11" s="41"/>
       <c r="Q11" s="40"/>
@@ -13413,32 +12177,32 @@
     </row>
     <row r="12" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
       <c r="E12" s="42" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G12" s="42" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="H12" s="42" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I12" s="42" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="J12" s="42" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="K12" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L12" s="40"/>
       <c r="M12" s="42" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="N12" s="41" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="O12" s="41"/>
       <c r="P12" s="41"/>
@@ -13449,35 +12213,35 @@
     </row>
     <row r="13" spans="5:20" ht="53.4" x14ac:dyDescent="0.3">
       <c r="E13" s="51" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="G13" s="42" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="H13" s="42" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="I13" s="42" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J13" s="42" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="K13" s="42" t="s">
         <v>77</v>
       </c>
       <c r="L13" s="40"/>
       <c r="M13" s="46" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="N13" s="46" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="O13" s="46" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="P13" s="41"/>
       <c r="Q13" s="40"/>
@@ -13490,32 +12254,32 @@
         <v>57</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="G14" s="42" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="H14" s="42" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="I14" s="42" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="J14" s="42" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="K14" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L14" s="40"/>
       <c r="M14" s="46" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="N14" s="41" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="O14" s="46" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P14" s="41"/>
       <c r="Q14" s="40"/>
@@ -13525,33 +12289,33 @@
     </row>
     <row r="15" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="E15" s="42" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="G15" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="I15" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="H15" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="I15" s="42" t="s">
-        <v>223</v>
-      </c>
       <c r="J15" s="42" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K15" s="42" t="s">
         <v>46</v>
       </c>
       <c r="L15" s="40"/>
       <c r="M15" s="42" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="N15" s="41"/>
       <c r="O15" s="52" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="P15" s="41"/>
       <c r="Q15" s="40"/>
@@ -13561,35 +12325,35 @@
     </row>
     <row r="16" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
       <c r="E16" s="53" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="F16" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="G16" s="49" t="s">
+        <v>220</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>238</v>
+      </c>
+      <c r="I16" s="49" t="s">
         <v>228</v>
       </c>
-      <c r="G16" s="49" t="s">
-        <v>225</v>
-      </c>
-      <c r="H16" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>233</v>
-      </c>
       <c r="J16" s="49" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="K16" s="42" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="L16" s="40"/>
       <c r="M16" s="41" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="N16" s="41" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="O16" s="41" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="P16" s="41"/>
       <c r="Q16" s="40"/>
@@ -13599,35 +12363,35 @@
     </row>
     <row r="17" spans="5:20" ht="129.6" x14ac:dyDescent="0.3">
       <c r="E17" s="42" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="F17" s="42" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="G17" s="42" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H17" s="42" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I17" s="42" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J17" s="42" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="K17" s="42" t="s">
         <v>91</v>
       </c>
       <c r="L17" s="40"/>
       <c r="M17" s="41" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="N17" s="41" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="O17" s="41" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="P17" s="41"/>
       <c r="Q17" s="40"/>

--- a/DarkJargon_SoK_taxonomy_tables.xlsx
+++ b/DarkJargon_SoK_taxonomy_tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Projekte\DarkJargon-SOK-USENIX26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABDCB65F-9197-4D48-81C4-2DA6E3C44108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B5B201-D1ED-4C43-A955-0F247CAD0A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="3" activeTab="5" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="2" activeTab="2" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -25,10 +25,6 @@
     <sheet name="resources_tax" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
-  </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -46,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="522">
   <si>
     <t>Approaches</t>
   </si>
@@ -478,12 +474,6 @@
   </si>
   <si>
     <t>Grand Total</t>
-  </si>
-  <si>
-    <t>Count of type simp</t>
-  </si>
-  <si>
-    <t>Column Labels</t>
   </si>
   <si>
     <t>approach</t>
@@ -2744,27 +2734,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2779,78 +2754,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFABABAB"/>
       </left>
       <right/>
       <top style="thin">
         <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFABABAB"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFABABAB"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFABABAB"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFABABAB"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -2886,7 +2795,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2925,25 +2834,14 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -3502,16 +3400,16 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>3</c:v>
@@ -5985,10 +5883,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>232229</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>120354</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>497273</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>173362</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3242129" cy="2066256"/>
     <xdr:graphicFrame macro="">
@@ -6957,148 +6855,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="" refreshedDate="0" createdVersion="8" refreshedVersion="8" recordCount="0" xr:uid="{811EC0CE-2390-4155-AA19-41504D6A7F8D}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A9" sheet="publication"/>
-  </cacheSource>
-  <cacheFields count="13">
-    <cacheField name="type simp" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="year" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="title" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="conference" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="journal" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="preprint" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="not academic" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="name of pub" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="year-month" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="peer reviewd" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="library" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="type" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="focused on" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9E0E3A19-2E91-465C-B843-2F7B3E67EE98}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0">
-  <location ref="A3:D15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="13">
-    <pivotField axis="axisCol" dataField="1" compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" showAll="0" includeNewItemsInFilter="1">
-      <items count="1">
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <dataFields count="1">
-    <dataField name="Count of type simp" fld="0" subtotal="count" baseField="0" baseItem="1048828"/>
-  </dataFields>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7887,7 +7643,7 @@
     </row>
     <row r="17" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -7914,7 +7670,7 @@
     </row>
     <row r="18" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -7956,85 +7712,85 @@
   <sheetData>
     <row r="1" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="H1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55" t="s">
-        <v>393</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
+      <c r="A2" s="46" t="s">
+        <v>391</v>
+      </c>
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
     </row>
     <row r="3" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C3" s="1">
         <v>2022</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="E3" s="32" t="s">
-        <v>361</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="J3" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -8042,31 +7798,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C4" s="1">
         <v>2017</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -8074,34 +7830,34 @@
         <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C5" s="1">
         <v>2019</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K5" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -8109,66 +7865,66 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C6" s="1">
         <v>2017</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="E6" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>396</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C7" s="1">
         <v>2015</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>372</v>
-      </c>
       <c r="H7" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="K7" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -8176,28 +7932,28 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C8" s="1">
         <v>2007</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E8" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K8" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -8209,338 +7965,338 @@
         <v>2018</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="K9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="47" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="47" t="s">
         <v>403</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="K9" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="56" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="56" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1">
         <v>2021</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="F11" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I11" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>2018</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="E12" s="32" t="s">
+        <v>381</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G12" t="s">
+        <v>158</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="K12" t="s">
         <v>408</v>
       </c>
-      <c r="F12" s="1" t="s">
+    </row>
+    <row r="13" spans="1:12" s="46" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="46" t="s">
         <v>409</v>
-      </c>
-      <c r="G12" t="s">
-        <v>160</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="K12" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="55" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="55" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C14" s="1">
         <v>2023</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C15" s="1">
         <v>2016</v>
       </c>
       <c r="D15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E15" t="s">
+        <v>412</v>
+      </c>
+      <c r="F15" t="s">
+        <v>413</v>
+      </c>
+      <c r="G15" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="J15" t="s">
         <v>414</v>
-      </c>
-      <c r="F15" t="s">
-        <v>415</v>
-      </c>
-      <c r="G15" t="s">
-        <v>160</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="J15" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C16" s="1">
         <v>2022</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>421</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="B17" s="34" t="s">
-        <v>424</v>
+        <v>421</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>422</v>
       </c>
       <c r="C17" s="1">
         <v>2024</v>
       </c>
-      <c r="D17" s="33" t="s">
-        <v>356</v>
+      <c r="D17" s="24" t="s">
+        <v>354</v>
       </c>
       <c r="E17" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>427</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B18" s="34"/>
+        <v>400</v>
+      </c>
+      <c r="B18" s="25"/>
       <c r="C18" s="1">
         <v>2018</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E18" t="s">
+        <v>426</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>428</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C19" s="1">
         <v>2024</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E19" t="s">
+        <v>431</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>436</v>
-      </c>
       <c r="J19" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C20" s="1">
         <v>2017</v>
       </c>
       <c r="D20" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C21" s="1">
         <v>2024</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>445</v>
       </c>
     </row>
   </sheetData>
@@ -8577,25 +8333,25 @@
     <row r="1" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="J1" s="7" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>32</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>33</v>
@@ -8622,25 +8378,25 @@
     <row r="2" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="J2" s="11" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N2" s="11" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>100</v>
@@ -8661,29 +8417,29 @@
         <v>46</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="J3" s="11" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="K3" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>493</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>495</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>221</v>
-      </c>
       <c r="N3" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>66</v>
@@ -8704,7 +8460,7 @@
         <v>46</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -8713,25 +8469,25 @@
     <row r="4" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="J4" s="11" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="N4" s="11" t="s">
         <v>117</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>49</v>
@@ -8751,8 +8507,8 @@
       <c r="V4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="W4" s="36" t="s">
-        <v>481</v>
+      <c r="W4" s="27" t="s">
+        <v>479</v>
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -8761,25 +8517,25 @@
     <row r="5" spans="1:26" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="J5" s="11" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>93</v>
@@ -8799,8 +8555,8 @@
       <c r="V5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="W5" s="36" t="s">
-        <v>482</v>
+      <c r="W5" s="27" t="s">
+        <v>480</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -8809,25 +8565,25 @@
     <row r="6" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="J6" s="11" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q6" s="11" t="s">
         <v>118</v>
@@ -8848,7 +8604,7 @@
         <v>46</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -8857,25 +8613,25 @@
     <row r="7" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="J7" s="11" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="K7" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>494</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="N7" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="L7" s="11" t="s">
-        <v>496</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>214</v>
-      </c>
       <c r="O7" s="11" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="Q7" s="11" t="s">
         <v>41</v>
@@ -8895,8 +8651,8 @@
       <c r="V7" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="W7" s="35" t="s">
-        <v>484</v>
+      <c r="W7" s="26" t="s">
+        <v>482</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -8905,25 +8661,25 @@
     <row r="8" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="J8" s="11" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="N8" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>112</v>
@@ -8944,7 +8700,7 @@
         <v>77</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -8953,25 +8709,25 @@
     <row r="9" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="J9" s="11" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>99</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q9" s="11" t="s">
         <v>72</v>
@@ -8979,7 +8735,7 @@
       <c r="R9" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="S9" s="37" t="s">
+      <c r="S9" s="28" t="s">
         <v>74</v>
       </c>
       <c r="T9" s="11" t="s">
@@ -8992,7 +8748,7 @@
         <v>77</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
@@ -9001,33 +8757,33 @@
     <row r="10" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="J10" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="K10" s="37" t="s">
-        <v>223</v>
+        <v>471</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>221</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="N10" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="O10" s="37" t="s">
-        <v>506</v>
-      </c>
-      <c r="P10" s="37" t="s">
-        <v>297</v>
-      </c>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
+        <v>238</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>504</v>
+      </c>
+      <c r="P10" s="28" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
@@ -9035,25 +8791,25 @@
     <row r="11" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="J11" s="11" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="K11" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>496</v>
+      </c>
+      <c r="M11" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="L11" s="11" t="s">
-        <v>498</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>225</v>
-      </c>
       <c r="N11" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>79</v>
@@ -9073,7 +8829,7 @@
       <c r="V11" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W11" s="35" t="s">
+      <c r="W11" s="26" t="s">
         <v>83</v>
       </c>
       <c r="X11" s="1"/>
@@ -9082,25 +8838,25 @@
     </row>
     <row r="12" spans="1:26" ht="331.2" x14ac:dyDescent="0.3">
       <c r="J12" s="11" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="Q12" s="11" t="s">
         <v>106</v>
@@ -9111,7 +8867,7 @@
       <c r="S12" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="T12" s="37" t="s">
+      <c r="T12" s="28" t="s">
         <v>109</v>
       </c>
       <c r="U12" s="11" t="s">
@@ -9121,7 +8877,7 @@
         <v>46</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -9131,25 +8887,25 @@
       <c r="A13" s="6"/>
       <c r="I13" s="10"/>
       <c r="J13" s="11" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="Q13" s="11" t="s">
         <v>128</v>
@@ -9176,25 +8932,25 @@
     <row r="14" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="J14" s="11" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="Q14" s="11" t="s">
         <v>54</v>
@@ -9215,7 +8971,7 @@
         <v>46</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -9224,25 +8980,25 @@
     <row r="15" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="J15" s="11" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q15" s="11" t="s">
         <v>60</v>
@@ -9263,7 +9019,7 @@
         <v>46</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -9272,33 +9028,33 @@
     <row r="16" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="J16" s="11" t="s">
-        <v>475</v>
-      </c>
-      <c r="K16" s="37" t="s">
-        <v>223</v>
-      </c>
-      <c r="L16" s="37" t="s">
-        <v>494</v>
+        <v>473</v>
+      </c>
+      <c r="K16" s="28" t="s">
+        <v>221</v>
+      </c>
+      <c r="L16" s="28" t="s">
+        <v>492</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="N16" s="37" t="s">
-        <v>228</v>
-      </c>
-      <c r="O16" s="37" t="s">
-        <v>504</v>
-      </c>
-      <c r="P16" s="37" t="s">
-        <v>291</v>
-      </c>
-      <c r="Q16" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="N16" s="28" t="s">
+        <v>226</v>
+      </c>
+      <c r="O16" s="28" t="s">
+        <v>502</v>
+      </c>
+      <c r="P16" s="28" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q16" s="28" t="s">
         <v>123</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>521</v>
-      </c>
-      <c r="S16" s="37" t="s">
+        <v>519</v>
+      </c>
+      <c r="S16" s="28" t="s">
         <v>124</v>
       </c>
       <c r="T16" s="11" t="s">
@@ -9311,7 +9067,7 @@
         <v>77</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
@@ -9320,25 +9076,25 @@
     <row r="17" spans="1:26" ht="216" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="J17" s="11" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>86</v>
@@ -9359,7 +9115,7 @@
         <v>91</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -9749,43 +9505,43 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C1" t="s">
         <v>244</v>
       </c>
-      <c r="C1" t="s">
-        <v>246</v>
-      </c>
       <c r="D1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F1" t="s">
         <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="193.8" x14ac:dyDescent="0.3">
@@ -9793,10 +9549,10 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>252</v>
+        <v>247</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>250</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -9805,10 +9561,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -9817,119 +9573,119 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B6" t="s">
-        <v>256</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="E6" s="1">
         <v>0.6</v>
       </c>
       <c r="F6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B7" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C7" s="30" t="s">
-        <v>265</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="F7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B8" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F8" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C9" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="D10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
-      </c>
-      <c r="C11" s="30" t="s">
-        <v>265</v>
+        <v>254</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>263</v>
       </c>
       <c r="E11" s="1">
         <v>0.31</v>
       </c>
       <c r="F11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B12" t="s">
-        <v>256</v>
-      </c>
-      <c r="C12" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="E12" s="1">
         <v>0.60560000000000003</v>
@@ -9937,189 +9693,189 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C13" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="E13" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="C14" s="30"/>
+      <c r="C14" s="21"/>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B15" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G15" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>257</v>
+        <v>254</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>255</v>
       </c>
       <c r="E16" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F16" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="C17" s="30"/>
+      <c r="C17" s="21"/>
       <c r="D17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F18" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B20" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" t="s">
+        <v>280</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B20" t="s">
-        <v>243</v>
-      </c>
-      <c r="C20" t="s">
-        <v>282</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>283</v>
-      </c>
       <c r="F20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="D21" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B22" t="s">
+        <v>284</v>
+      </c>
+      <c r="C22" t="s">
+        <v>286</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="B22" t="s">
-        <v>286</v>
-      </c>
-      <c r="C22" t="s">
-        <v>288</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>289</v>
-      </c>
       <c r="F22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B23" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E23" s="1">
         <v>94.3</v>
       </c>
       <c r="F23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C24" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -10140,7 +9896,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399DB999-9283-4751-BBD0-238C098D8C5B}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A3:D30"/>
+  <dimension ref="A19:D30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -10163,181 +9919,15 @@
     <col min="26" max="26" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="24"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="D4" s="25" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="16">
-        <v>2015</v>
-      </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="15">
-        <v>1</v>
-      </c>
-      <c r="D5" s="25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="17">
-        <v>2016</v>
-      </c>
-      <c r="B6" s="18">
-        <v>1</v>
-      </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="17">
-        <v>2017</v>
-      </c>
-      <c r="B7" s="18">
-        <v>1</v>
-      </c>
-      <c r="C7" s="19">
-        <v>2</v>
-      </c>
-      <c r="D7" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="17">
-        <v>2018</v>
-      </c>
-      <c r="B8" s="18">
-        <v>1</v>
-      </c>
-      <c r="C8" s="19">
-        <v>3</v>
-      </c>
-      <c r="D8" s="26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
-        <v>2019</v>
-      </c>
-      <c r="B9" s="18">
-        <v>1</v>
-      </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="17">
-        <v>2021</v>
-      </c>
-      <c r="B10" s="18">
-        <v>4</v>
-      </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="17">
-        <v>2022</v>
-      </c>
-      <c r="B11" s="18">
-        <v>1</v>
-      </c>
-      <c r="C11" s="19">
-        <v>2</v>
-      </c>
-      <c r="D11" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="17">
-        <v>2023</v>
-      </c>
-      <c r="B12" s="18">
-        <v>3</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="17">
-        <v>2024</v>
-      </c>
-      <c r="B13" s="18">
-        <v>4</v>
-      </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="26">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="17">
-        <v>2025</v>
-      </c>
-      <c r="B14" s="18">
-        <v>2</v>
-      </c>
-      <c r="C14" s="19">
-        <v>1</v>
-      </c>
-      <c r="D14" s="26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
-        <v>136</v>
-      </c>
-      <c r="B15" s="21">
-        <v>18</v>
-      </c>
-      <c r="C15" s="22">
-        <v>9</v>
-      </c>
-      <c r="D15" s="13">
-        <v>27</v>
-      </c>
-    </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>133</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
         <v>136</v>
@@ -10390,7 +9980,7 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -10412,7 +10002,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -10426,7 +10016,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -10473,15 +10063,15 @@
         <v>16</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10500,10 +10090,10 @@
   <sheetData>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
         <v>136</v>
@@ -10511,7 +10101,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -10522,7 +10112,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -10536,7 +10126,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B22">
         <v>5</v>
@@ -10547,7 +10137,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -10558,7 +10148,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -10569,7 +10159,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -10580,7 +10170,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -10594,7 +10184,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -10621,66 +10211,66 @@
   </cols>
   <sheetData>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="B17" s="26">
+      <c r="B19" s="17">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="B19" s="26">
-        <v>1</v>
-      </c>
-    </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="17">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="17">
         <v>4</v>
       </c>
     </row>
@@ -10702,29 +10292,29 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>508</v>
+      </c>
+      <c r="B1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C1" t="s">
         <v>510</v>
-      </c>
-      <c r="B1" t="s">
-        <v>511</v>
-      </c>
-      <c r="C1" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>75</v>
@@ -10732,18 +10322,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -10751,7 +10341,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>75</v>
@@ -10759,29 +10349,29 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>44</v>
@@ -10789,10 +10379,10 @@
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
@@ -10800,7 +10390,7 @@
     </row>
     <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>75</v>
@@ -10811,40 +10401,40 @@
     </row>
     <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>44</v>
@@ -10855,21 +10445,21 @@
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
@@ -10898,43 +10488,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>155</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>133</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>134</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10942,33 +10532,33 @@
         <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G2" s="1">
         <v>2025</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="18">
         <v>45870</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L2" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10976,33 +10566,33 @@
         <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G3" s="1">
         <v>2023</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="18">
         <v>45108</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L3" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11010,33 +10600,33 @@
         <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G4" s="1">
         <v>2022</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="18">
         <v>44593</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11044,33 +10634,33 @@
         <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="F5" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="G5" s="28">
+      <c r="F5" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" s="19">
         <v>2025</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="18">
         <v>45839</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L5" s="1" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11078,33 +10668,33 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G6" s="1">
         <v>2024</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="18">
         <v>45413</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11112,33 +10702,33 @@
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="F7" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="G7" s="28">
+      <c r="F7" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="G7" s="19">
         <v>2021</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="18">
         <v>44197</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L7" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11148,29 +10738,29 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G8" s="1">
         <v>2024</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="18">
         <v>45352</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11178,33 +10768,33 @@
         <v>111</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G9" s="1">
         <v>2016</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="18">
         <v>42614</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L9" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11212,33 +10802,33 @@
         <v>116</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G10" s="1">
         <v>2021</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="18">
         <v>44317</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L10" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11246,33 +10836,33 @@
         <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G11" s="1">
         <v>2023</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="18">
         <v>45139</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K11" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L11" s="1" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11280,67 +10870,67 @@
         <v>122</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G12" s="1">
         <v>2017</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="18">
         <v>42856</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="K12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L12" s="1" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="45" t="s">
         <v>127</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G13" s="1">
         <v>2024</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="18">
         <v>45383</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="K13" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L13" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11348,33 +10938,33 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G14" s="1">
         <v>2023</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="18">
         <v>45108</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L14" s="1" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11382,33 +10972,33 @@
         <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G15" s="1">
         <v>2018</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="18">
         <v>43313</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L15" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11417,64 +11007,64 @@
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G16" s="1">
         <v>2024</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="18">
         <v>45413</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K16" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="L16" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G17" s="1">
         <v>2021</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="20">
         <v>44378</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -11482,31 +11072,31 @@
         <v>3</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G18" s="1">
         <v>2017</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="20">
         <v>42826</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -11514,31 +11104,31 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G19" s="1">
         <v>2019</v>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="20">
         <v>43617</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -11546,31 +11136,31 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G20" s="1">
         <v>2017</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="18">
         <v>42979</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
@@ -11578,54 +11168,54 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G21" s="1">
         <v>2022</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="20">
         <v>44743</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E22" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G22" s="1">
         <v>2015</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="20">
         <v>43101</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -11633,7 +11223,7 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F23"/>
       <c r="G23" s="1">
@@ -11643,13 +11233,13 @@
         <v>2007</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -11657,27 +11247,27 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G24" s="1">
         <v>2018</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="20">
         <v>43101</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L24" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
-      <c r="H25" s="29"/>
+      <c r="H25" s="20"/>
       <c r="K25" s="1"/>
       <c r="M25" s="1"/>
     </row>
@@ -11686,7 +11276,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="32"/>
+      <c r="E27" s="23"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="K27" s="1"/>
@@ -11713,7 +11303,7 @@
       <c r="B30" s="2"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="32"/>
+      <c r="E30" s="23"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="K30" s="1"/>
@@ -11764,640 +11354,640 @@
   </cols>
   <sheetData>
     <row r="1" spans="5:20" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="38" t="s">
-        <v>518</v>
-      </c>
-      <c r="G1" s="38" t="s">
+      <c r="F1" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="G1" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="38" t="s">
-        <v>519</v>
-      </c>
-      <c r="I1" s="38" t="s">
+      <c r="H1" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="I1" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="38" t="s">
+      <c r="J1" s="29" t="s">
+        <v>298</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="31"/>
+      <c r="M1" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="N1" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="O1" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+    </row>
+    <row r="2" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="E2" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>228</v>
+      </c>
+      <c r="G2" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I2" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="K2" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L2" s="31"/>
+      <c r="M2" s="33" t="s">
+        <v>511</v>
+      </c>
+      <c r="N2" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>521</v>
+      </c>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="31"/>
+      <c r="R2" s="31"/>
+      <c r="S2" s="31"/>
+      <c r="T2" s="31"/>
+    </row>
+    <row r="3" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="E3" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>217</v>
+      </c>
+      <c r="G3" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="H3" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I3" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="J3" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="31"/>
+      <c r="M3" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="N3" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="O3" s="35" t="s">
+        <v>323</v>
+      </c>
+      <c r="P3" s="32"/>
+      <c r="Q3" s="31"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+    </row>
+    <row r="4" spans="5:20" ht="156.6" x14ac:dyDescent="0.3">
+      <c r="E4" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="K1" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="40"/>
-      <c r="M1" s="38" t="s">
+      <c r="I4" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="J4" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="K4" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L4" s="31"/>
+      <c r="M4" s="36" t="s">
+        <v>513</v>
+      </c>
+      <c r="N4" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="O4" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+    </row>
+    <row r="5" spans="5:20" ht="96.6" x14ac:dyDescent="0.3">
+      <c r="E5" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="G5" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>227</v>
+      </c>
+      <c r="I5" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="J5" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="K5" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L5" s="31"/>
+      <c r="M5" s="36" t="s">
+        <v>514</v>
+      </c>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="31"/>
+      <c r="T5" s="31"/>
+    </row>
+    <row r="6" spans="5:20" ht="288" x14ac:dyDescent="0.3">
+      <c r="E6" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="G6" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I6" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="J6" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="K6" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="31"/>
+      <c r="M6" s="37" t="s">
+        <v>248</v>
+      </c>
+      <c r="N6" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="O6" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+    </row>
+    <row r="7" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E7" s="33" t="s">
+        <v>307</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>515</v>
+      </c>
+      <c r="K7" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7" s="31"/>
+      <c r="M7" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="N7" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="O7" s="32" t="s">
+        <v>341</v>
+      </c>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31"/>
+      <c r="T7" s="31"/>
+    </row>
+    <row r="8" spans="5:20" ht="79.8" x14ac:dyDescent="0.3">
+      <c r="E8" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="G8" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>232</v>
+      </c>
+      <c r="I8" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="J8" s="29" t="s">
+        <v>254</v>
+      </c>
+      <c r="K8" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="31"/>
+      <c r="M8" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="N1" s="38" t="s">
+      <c r="N8" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="O1" s="41" t="s">
+      <c r="O8" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="31"/>
+      <c r="T8" s="31"/>
+    </row>
+    <row r="9" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="E9" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>225</v>
+      </c>
+      <c r="G9" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="I9" s="33" t="s">
+        <v>99</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="K9" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="L9" s="31"/>
+      <c r="M9" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="N9" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="31"/>
+      <c r="T9" s="31"/>
+    </row>
+    <row r="10" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E10" s="40" t="s">
+        <v>310</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="G10" s="33" t="s">
+        <v>218</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="I10" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="J10" s="40" t="s">
+        <v>295</v>
+      </c>
+      <c r="K10" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+    </row>
+    <row r="11" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="E11" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="G11" s="33" t="s">
+        <v>222</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>223</v>
+      </c>
+      <c r="I11" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="J11" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="K11" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="L11" s="31"/>
+      <c r="M11" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="N11" s="39" t="s">
+        <v>332</v>
+      </c>
+      <c r="O11" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+    </row>
+    <row r="12" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="E12" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="F12" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="G12" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="I12" s="33" t="s">
+        <v>231</v>
+      </c>
+      <c r="J12" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="K12" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L12" s="31"/>
+      <c r="M12" s="33" t="s">
+        <v>334</v>
+      </c>
+      <c r="N12" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+    </row>
+    <row r="13" spans="5:20" ht="53.4" x14ac:dyDescent="0.3">
+      <c r="E13" s="42" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="G13" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>237</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="J13" s="33" t="s">
+        <v>241</v>
+      </c>
+      <c r="K13" s="33" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="31"/>
+      <c r="M13" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="N13" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="O13" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+    </row>
+    <row r="14" spans="5:20" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="E14" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="G14" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="J14" s="33" t="s">
+        <v>297</v>
+      </c>
+      <c r="K14" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L14" s="31"/>
+      <c r="M14" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="N14" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="O14" s="37" t="s">
+        <v>325</v>
+      </c>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+    </row>
+    <row r="15" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="E15" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="J15" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="K15" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="L15" s="31"/>
+      <c r="M15" s="33" t="s">
+        <v>337</v>
+      </c>
+      <c r="N15" s="32"/>
+      <c r="O15" s="43" t="s">
+        <v>344</v>
+      </c>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="31"/>
+      <c r="T15" s="31"/>
+    </row>
+    <row r="16" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E16" s="44" t="s">
+        <v>315</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>221</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>226</v>
+      </c>
+      <c r="J16" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="L16" s="31"/>
+      <c r="M16" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="N16" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="O16" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+    </row>
+    <row r="17" spans="5:20" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="E17" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>235</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="I17" s="33" t="s">
+        <v>226</v>
+      </c>
+      <c r="J17" s="33" t="s">
+        <v>284</v>
+      </c>
+      <c r="K17" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="L17" s="31"/>
+      <c r="M17" s="32" t="s">
         <v>326</v>
       </c>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="40"/>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40"/>
-      <c r="T1" s="40"/>
-    </row>
-    <row r="2" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E2" s="42" t="s">
-        <v>305</v>
-      </c>
-      <c r="F2" s="42" t="s">
-        <v>230</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>231</v>
-      </c>
-      <c r="H2" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="J2" s="38" t="s">
-        <v>243</v>
-      </c>
-      <c r="K2" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L2" s="40"/>
-      <c r="M2" s="42" t="s">
-        <v>513</v>
-      </c>
-      <c r="N2" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="O2" s="41" t="s">
-        <v>523</v>
-      </c>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-    </row>
-    <row r="3" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E3" s="42" t="s">
-        <v>306</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="H3" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="J3" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="K3" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="40"/>
-      <c r="M3" s="41" t="s">
-        <v>514</v>
-      </c>
-      <c r="N3" s="41" t="s">
-        <v>330</v>
-      </c>
-      <c r="O3" s="44" t="s">
-        <v>325</v>
-      </c>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-    </row>
-    <row r="4" spans="5:20" ht="156.6" x14ac:dyDescent="0.3">
-      <c r="E4" s="42" t="s">
-        <v>307</v>
-      </c>
-      <c r="F4" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="G4" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="H4" s="42" t="s">
-        <v>302</v>
-      </c>
-      <c r="I4" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="J4" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="K4" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" s="40"/>
-      <c r="M4" s="45" t="s">
-        <v>515</v>
-      </c>
-      <c r="N4" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="O4" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="40"/>
-      <c r="R4" s="40"/>
-      <c r="S4" s="40"/>
-      <c r="T4" s="40"/>
-    </row>
-    <row r="5" spans="5:20" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="E5" s="42" t="s">
-        <v>284</v>
-      </c>
-      <c r="F5" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" s="42" t="s">
-        <v>229</v>
-      </c>
-      <c r="I5" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="J5" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="K5" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" s="40"/>
-      <c r="M5" s="45" t="s">
-        <v>516</v>
-      </c>
-      <c r="N5" s="41"/>
-      <c r="O5" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-    </row>
-    <row r="6" spans="5:20" ht="288" x14ac:dyDescent="0.3">
-      <c r="E6" s="42" t="s">
-        <v>308</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="H6" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>235</v>
-      </c>
-      <c r="J6" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="K6" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="40"/>
-      <c r="M6" s="46" t="s">
-        <v>250</v>
-      </c>
-      <c r="N6" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="O6" s="41" t="s">
-        <v>342</v>
-      </c>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="40"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="40"/>
-      <c r="T6" s="40"/>
-    </row>
-    <row r="7" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E7" s="42" t="s">
-        <v>309</v>
-      </c>
-      <c r="F7" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="H7" s="42" t="s">
-        <v>221</v>
-      </c>
-      <c r="I7" s="42" t="s">
-        <v>214</v>
-      </c>
-      <c r="J7" s="42" t="s">
-        <v>517</v>
-      </c>
-      <c r="K7" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="40"/>
-      <c r="M7" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="N7" s="41" t="s">
-        <v>250</v>
-      </c>
-      <c r="O7" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="P7" s="41"/>
-      <c r="Q7" s="40"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="40"/>
-      <c r="T7" s="40"/>
-    </row>
-    <row r="8" spans="5:20" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="E8" s="42" t="s">
-        <v>310</v>
-      </c>
-      <c r="F8" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="G8" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="H8" s="42" t="s">
-        <v>234</v>
-      </c>
-      <c r="I8" s="42" t="s">
-        <v>85</v>
-      </c>
-      <c r="J8" s="38" t="s">
-        <v>256</v>
-      </c>
-      <c r="K8" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="40"/>
-      <c r="M8" s="47" t="s">
-        <v>323</v>
-      </c>
-      <c r="N8" s="47" t="s">
-        <v>322</v>
-      </c>
-      <c r="O8" s="41" t="s">
-        <v>344</v>
-      </c>
-      <c r="P8" s="41"/>
-      <c r="Q8" s="40"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-    </row>
-    <row r="9" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="E9" s="42" t="s">
-        <v>311</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="H9" s="42" t="s">
-        <v>222</v>
-      </c>
-      <c r="I9" s="42" t="s">
-        <v>99</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>324</v>
-      </c>
-      <c r="K9" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="L9" s="40"/>
-      <c r="M9" s="41" t="s">
-        <v>332</v>
-      </c>
-      <c r="N9" s="48" t="s">
-        <v>335</v>
-      </c>
-      <c r="O9" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="40"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-    </row>
-    <row r="10" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E10" s="49" t="s">
-        <v>312</v>
-      </c>
-      <c r="F10" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>220</v>
-      </c>
-      <c r="H10" s="42" t="s">
-        <v>240</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>228</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>297</v>
-      </c>
-      <c r="K10" s="49" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="50"/>
-      <c r="O10" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="40"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-    </row>
-    <row r="11" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="E11" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="F11" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>224</v>
-      </c>
-      <c r="H11" s="42" t="s">
-        <v>225</v>
-      </c>
-      <c r="I11" s="42" t="s">
-        <v>226</v>
-      </c>
-      <c r="J11" s="42" t="s">
-        <v>324</v>
-      </c>
-      <c r="K11" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="L11" s="40"/>
-      <c r="M11" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="N11" s="48" t="s">
-        <v>334</v>
-      </c>
-      <c r="O11" s="41" t="s">
-        <v>345</v>
-      </c>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="40"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-    </row>
-    <row r="12" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E12" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="F12" s="42" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="42" t="s">
-        <v>236</v>
-      </c>
-      <c r="H12" s="42" t="s">
-        <v>232</v>
-      </c>
-      <c r="I12" s="42" t="s">
-        <v>233</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>298</v>
-      </c>
-      <c r="K12" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L12" s="40"/>
-      <c r="M12" s="42" t="s">
-        <v>336</v>
-      </c>
-      <c r="N12" s="41" t="s">
-        <v>337</v>
-      </c>
-      <c r="O12" s="41"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="40"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="40"/>
-      <c r="T12" s="40"/>
-    </row>
-    <row r="13" spans="5:20" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="E13" s="51" t="s">
-        <v>315</v>
-      </c>
-      <c r="F13" s="42" t="s">
-        <v>212</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>215</v>
-      </c>
-      <c r="H13" s="42" t="s">
-        <v>239</v>
-      </c>
-      <c r="I13" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>243</v>
-      </c>
-      <c r="K13" s="42" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" s="40"/>
-      <c r="M13" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="N13" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="O13" s="46" t="s">
-        <v>338</v>
-      </c>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="40"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="40"/>
-      <c r="T13" s="40"/>
-    </row>
-    <row r="14" spans="5:20" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="E14" s="42" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="G14" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="H14" s="42" t="s">
-        <v>303</v>
-      </c>
-      <c r="I14" s="42" t="s">
-        <v>301</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>299</v>
-      </c>
-      <c r="K14" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="40"/>
-      <c r="M14" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="N14" s="41" t="s">
-        <v>390</v>
-      </c>
-      <c r="O14" s="46" t="s">
-        <v>327</v>
-      </c>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-    </row>
-    <row r="15" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E15" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="F15" s="42" t="s">
-        <v>242</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>213</v>
-      </c>
-      <c r="H15" s="42" t="s">
-        <v>217</v>
-      </c>
-      <c r="I15" s="42" t="s">
-        <v>218</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="K15" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="40"/>
-      <c r="M15" s="42" t="s">
-        <v>339</v>
-      </c>
-      <c r="N15" s="41"/>
-      <c r="O15" s="52" t="s">
-        <v>346</v>
-      </c>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="40"/>
-      <c r="R15" s="40"/>
-      <c r="S15" s="40"/>
-      <c r="T15" s="40"/>
-    </row>
-    <row r="16" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E16" s="53" t="s">
-        <v>317</v>
-      </c>
-      <c r="F16" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>220</v>
-      </c>
-      <c r="H16" s="42" t="s">
-        <v>238</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>228</v>
-      </c>
-      <c r="J16" s="49" t="s">
-        <v>291</v>
-      </c>
-      <c r="K16" s="42" t="s">
-        <v>319</v>
-      </c>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="N16" s="41" t="s">
-        <v>341</v>
-      </c>
-      <c r="O16" s="41" t="s">
-        <v>275</v>
-      </c>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="40"/>
-      <c r="T16" s="40"/>
-    </row>
-    <row r="17" spans="5:20" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="E17" s="42" t="s">
-        <v>318</v>
-      </c>
-      <c r="F17" s="42" t="s">
-        <v>241</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>237</v>
-      </c>
-      <c r="H17" s="42" t="s">
-        <v>304</v>
-      </c>
-      <c r="I17" s="42" t="s">
-        <v>228</v>
-      </c>
-      <c r="J17" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="K17" s="42" t="s">
-        <v>91</v>
-      </c>
-      <c r="L17" s="40"/>
-      <c r="M17" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="N17" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="O17" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="40"/>
-      <c r="S17" s="40"/>
-      <c r="T17" s="40"/>
+      <c r="N17" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="O17" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
     </row>
     <row r="18" spans="5:20" x14ac:dyDescent="0.3">
       <c r="E18" s="2"/>

--- a/DarkJargon_SoK_taxonomy_tables.xlsx
+++ b/DarkJargon_SoK_taxonomy_tables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Projekte\DarkJargon-SOK-USENIX26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B5B201-D1ED-4C43-A955-0F247CAD0A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C5A6C-99FE-49D5-B057-CE0D9F29AF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" firstSheet="2" activeTab="2" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21360" firstSheet="1" activeTab="8" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="938" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="509">
   <si>
     <t>Approaches</t>
   </si>
@@ -356,9 +356,6 @@
     <t>FOR DRUG EUPHEMISMIN ONLY "Drug Jargon"
 -&gt; Given a sentence and a word in the sentence, determine whether
 the word is used as a drug jargon in the specific contex (benigm meaning or not)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Reddit Drug corpus (Zhu et al) (surface discussions), silk Road Forum corpus (Branwen et al) (dark web discussions); drug slang report (Drug Enforcement Administration) --&gt; list of 46 explicit drug terms   </t>
   </si>
   <si>
     <t>reddit drug: 0.64 f1, silk road forum: 0.63 f1</t>
@@ -632,9 +629,6 @@
     <t>An Unsupervised Detection Framework for Chinese Jargons in the Darknet</t>
   </si>
   <si>
-    <t>CAN’T SAY CANT?</t>
-  </si>
-  <si>
     <t>dark jargon, slang, argot, secret language</t>
   </si>
   <si>
@@ -698,15 +692,9 @@
     <t>O1, O3</t>
   </si>
   <si>
-    <t>T1, T2, T4</t>
-  </si>
-  <si>
     <t>S4</t>
   </si>
   <si>
-    <t>T2, T4</t>
-  </si>
-  <si>
     <t>O1, O4</t>
   </si>
   <si>
@@ -719,9 +707,6 @@
     <t>O1, O2</t>
   </si>
   <si>
-    <t>T1-T4</t>
-  </si>
-  <si>
     <t>M3, M4, M5</t>
   </si>
   <si>
@@ -731,9 +716,6 @@
     <t>O1, O3, O4</t>
   </si>
   <si>
-    <t>T1, T2, T3, T4</t>
-  </si>
-  <si>
     <t>M1, M3, M5, M8</t>
   </si>
   <si>
@@ -752,9 +734,6 @@
     <t>O1</t>
   </si>
   <si>
-    <t>T1 - T4</t>
-  </si>
-  <si>
     <t>M3, M4, M5, M8</t>
   </si>
   <si>
@@ -767,12 +746,6 @@
     <t>S1, S4</t>
   </si>
   <si>
-    <t>T2-T4, (T1)</t>
-  </si>
-  <si>
-    <t>T3, T4, (T1)</t>
-  </si>
-  <si>
     <t>M1, M4, M5, M7, M8</t>
   </si>
   <si>
@@ -782,9 +755,6 @@
     <t>M1, M5, M6, M8</t>
   </si>
   <si>
-    <t>O1-O3</t>
-  </si>
-  <si>
     <t>O3, O4</t>
   </si>
   <si>
@@ -803,18 +773,6 @@
     <t>P, R, F1</t>
   </si>
   <si>
-    <t xml:space="preserve"> Drugs:P=0.666, R=0.620, F1=0.642,  Silk Road P=0.581, R=0.693, F1=0.632</t>
-  </si>
-  <si>
-    <t>\cite{darkbert}</t>
-  </si>
-  <si>
-    <t>\cite{selfsupervised}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\cite{yuan2018} </t>
-  </si>
-  <si>
     <t>drugs: p=0.5460, R=0.5705 F1=0.5580 silk road: P=0.4790 R=0.5793 F1=0.5244</t>
   </si>
   <si>
@@ -839,18 +797,6 @@
     <t>MRR</t>
   </si>
   <si>
-    <t>\cite{seyler} (KL-Divergence)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\cite{darkbert} </t>
-  </si>
-  <si>
-    <t>\cite{syntactic}</t>
-  </si>
-  <si>
-    <t>\cite{contentcracks}</t>
-  </si>
-  <si>
     <t>Artificial DJ: 0.909, DJ: 0.892</t>
   </si>
   <si>
@@ -860,78 +806,42 @@
     <t>drugs: 0.50, weapons: 0.40, sex: 0.70</t>
   </si>
   <si>
-    <t>\cite{yuan2018}</t>
-  </si>
-  <si>
     <t>drugs: 0.30, weapons: 0.20, sex: 0.10</t>
   </si>
   <si>
-    <t>\cite{euphemismident}</t>
-  </si>
-  <si>
-    <t>\cite{chineseunderground} (Word2Vec CBOW)</t>
-  </si>
-  <si>
-    <t>\cite{unsupervised}</t>
-  </si>
-  <si>
-    <t>\cite{novelcrossdomain}</t>
-  </si>
-  <si>
-    <t>\cite{chineseunderground}</t>
-  </si>
-  <si>
     <t>0.17/0.29</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>\cite{darkjargonnet}</t>
-  </si>
-  <si>
     <t>P, R</t>
   </si>
   <si>
     <t>R 77.2, P 91</t>
   </si>
   <si>
-    <t>\cite{mect}</t>
-  </si>
-  <si>
     <t>P = 0.35, R = 0.31, and F1 = 0.33</t>
   </si>
   <si>
-    <t>\cite{argot}</t>
-  </si>
-  <si>
     <t>accuracy, F1</t>
   </si>
   <si>
     <t>acc = 0.67, F1= 0.654</t>
   </si>
   <si>
-    <t>seyler</t>
-  </si>
-  <si>
     <t>acc = 0.723, F1= 0.703</t>
   </si>
   <si>
     <t>E3</t>
   </si>
   <si>
-    <t>\cite{cantsaycant}</t>
-  </si>
-  <si>
     <t>Accuracy</t>
   </si>
   <si>
     <t>Interpretation ChatGPT-3.5=45.38, Detection: Oneshot: BARD=65.91, Zeroshot: New Bing=50</t>
   </si>
   <si>
-    <t>\cite{klingon}</t>
-  </si>
-  <si>
     <t>E4</t>
   </si>
   <si>
@@ -941,9 +851,6 @@
     <t>E2 + E4</t>
   </si>
   <si>
-    <t xml:space="preserve">\cite{twostep} </t>
-  </si>
-  <si>
     <t>P = 0.991, R = 0.991, F1 = 0.991</t>
   </si>
   <si>
@@ -974,57 +881,15 @@
     <t>M5, M8, M9, (M3)</t>
   </si>
   <si>
-    <t>contentcracks</t>
-  </si>
-  <si>
-    <t>darkbert</t>
-  </si>
-  <si>
-    <t>syntactic</t>
-  </si>
-  <si>
     <t>selfsupervised</t>
   </si>
   <si>
-    <t>EuphemismIdent</t>
-  </si>
-  <si>
-    <t>chineseunderground</t>
-  </si>
-  <si>
-    <t>unsupervised</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darkjargonnet </t>
-  </si>
-  <si>
-    <t>NovelCrossDomain</t>
-  </si>
-  <si>
-    <t>ReadingThievesCant</t>
-  </si>
-  <si>
-    <t>mect</t>
-  </si>
-  <si>
-    <t>cantsaycant</t>
-  </si>
-  <si>
-    <t>klingon</t>
-  </si>
-  <si>
-    <t>twostep</t>
-  </si>
-  <si>
     <t>5 chinese, 1 korean</t>
   </si>
   <si>
     <t>GT eval</t>
   </si>
   <si>
-    <t>raw data eval+M1:R31</t>
-  </si>
-  <si>
     <t>manually selected 70 typical Chinese underground jargons</t>
   </si>
   <si>
@@ -1043,19 +908,6 @@
     <t>Hackforum subset of CrimeBB dataset, with 500 words annotated</t>
   </si>
   <si>
-    <t>\cite{darkbert+ regular bul-
-letin board articles from AIHub</t>
-  </si>
-  <si>
-    <t>Two evaluation datasets based on the raw data, manually annotated 1000 secntences each</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sample drug dataset of \cite{selfsupervised} </t>
-  </si>
-  <si>
-    <t>Drugs: \cite{dea}, weapons:onlineslangdictionary \cite{onlineslangdictionary}, slangpedia, urban thesaurus \cite{urbanthesaurus}, sex: \cite{onlineslangdictionary}</t>
-  </si>
-  <si>
     <t>DC-Dataset (E2),  200 detected samples (E4)</t>
   </si>
   <si>
@@ -1069,12 +921,6 @@
   </si>
   <si>
     <t xml:space="preserve">dark corpora &amp; benigm corpora </t>
-  </si>
-  <si>
-    <t>\cite{dea}, cybercrime marketplace product list \cite{cybercrimemarket}</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MNGG Dataset \cite{mect}</t>
   </si>
   <si>
     <t>Cant-Dataset</t>
@@ -2543,43 +2389,9 @@
     <t>Secondary</t>
   </si>
   <si>
-    <t>reddit drug corpus \cite{selfsupervised}, silk road Forum corpus \cite{dnmArchives}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ft with CoDA \cite{coda}, sample drug dataset by  \cite{selfsupervised} </t>
-  </si>
-  <si>
-    <t>drug: drug dataset by \cite{selfsupervised}, weapons: weapons dataset by \cite{yuan2018}, sex: sexuality dataset by \cite{selfsupervised}</t>
-  </si>
-  <si>
-    <t>dark corpus \cite{yuan2018}, clean corpus: web scrape of  1.2 million reddit threads</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>E2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Objective</t>
   </si>
   <si>
-    <t>Model</t>
-  </si>
-  <si>
     <t xml:space="preserve">E2 </t>
   </si>
   <si>
@@ -2590,13 +2402,146 @@
   </si>
   <si>
     <t>46 DEA terms (for automatic labeling), raw data labelled</t>
+  </si>
+  <si>
+    <t>drugs: P=0.666, R=0.620, F1=0.642,  Silk Road P=0.581, R=0.693, F1=0.632</t>
+  </si>
+  <si>
+    <t>Song et. Al (2025)</t>
+  </si>
+  <si>
+    <t>Jin et al. (2023)</t>
+  </si>
+  <si>
+    <t>Yuan et al. (2018)</t>
+  </si>
+  <si>
+    <t>Zhu et al. (2021)</t>
+  </si>
+  <si>
+    <t>Zhao et al. (2016)</t>
+  </si>
+  <si>
+    <t>Thao et al. (2018) (Word2Vec CBOW)</t>
+  </si>
+  <si>
+    <t>Huang et al. (2023)</t>
+  </si>
+  <si>
+    <t>Hughes et al. (2023)</t>
+  </si>
+  <si>
+    <t>Seyler et al. (2021) (KL-Divergence)</t>
+  </si>
+  <si>
+    <t>Seyler et al. (2021)  (KL-Divergence)</t>
+  </si>
+  <si>
+    <t>Li et al. (2024)</t>
+  </si>
+  <si>
+    <t>Ke et al. (2024)</t>
+  </si>
+  <si>
+    <t>Seyler et al (2021)</t>
+  </si>
+  <si>
+    <t>Ke et al. (2022)</t>
+  </si>
+  <si>
+    <t>Hu et al. (2024)</t>
+  </si>
+  <si>
+    <t>Ji et al. (2024)</t>
+  </si>
+  <si>
+    <t>Yuang et al. (2017)</t>
+  </si>
+  <si>
+    <t>Kim et al. (2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Reddit Drug corpus (Zhu et al. : surface web  discussions, silk Road Forum corpus (Branwen et al., dark web discussions; drug slang report (DEA) --&gt; list of 46 explicit drug terms   </t>
+  </si>
+  <si>
+    <t>Can't say cant?</t>
+  </si>
+  <si>
+    <t>Covering Cracks in Content Moderation: Delexicalized Distant Supervision for Illicit Drug Jargon Detection</t>
+  </si>
+  <si>
+    <t>DarkBert</t>
+  </si>
+  <si>
+    <t>Chinese underground market jargon analysis based on unsupervised learning</t>
+  </si>
+  <si>
+    <t>DarkJargon.net: A Platform for Understanding Underground Conversation with Latent Meaning</t>
+  </si>
+  <si>
+    <t>Reading Thieves' Cant: Automatically Identifying and Understanding Dark Jargons from Cybercrime Marketplaces</t>
+  </si>
+  <si>
+    <t>Argot as a Trust Signal: Slang, Jargon &amp; Reputation on a Large Cybercrime Forum</t>
+  </si>
+  <si>
+    <t>Can't say cant? Measuring and Reasoning of Dark Jargons in Large Language Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MNGG Dataset </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MNGG Dataset</t>
+  </si>
+  <si>
+    <t>darkbert+ regular bul-
+letin board articles from AIHub</t>
+  </si>
+  <si>
+    <t>dea, cybercrime marketplace product list</t>
+  </si>
+  <si>
+    <t>raw data eval</t>
+  </si>
+  <si>
+    <t>Two evaluation datasets based on the raw data, manually annotated 1000 sentences each</t>
+  </si>
+  <si>
+    <t>reddit drug corpus (selfsupervised), silk road Forum corpus by dnmArchives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ft with CoDA, sample of drug dataset by  (selfsupervised) </t>
+  </si>
+  <si>
+    <t>sample of drug dataset of (selfsupervised})</t>
+  </si>
+  <si>
+    <t>drug: drug dataset by selfsupervised, weapons: weapons dataset by yuan, sex: sexuality dataset by selfsupervised</t>
+  </si>
+  <si>
+    <t>datasets by selfsupervised</t>
+  </si>
+  <si>
+    <t>dark corpus by yuan, clean corpus: web scrape of  1.2 million reddit threads</t>
+  </si>
+  <si>
+    <t>Drugs: dea, weapons:onlineslangdictionary, slangpedia, urban thesaurus, sex: onlineslangdictionary</t>
+  </si>
+  <si>
+    <t>dataset by selfsupervised</t>
+  </si>
+  <si>
+    <t>dataset selfsupervised</t>
+  </si>
+  <si>
+    <t>dataset m by yuan</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -2628,13 +2573,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos Display"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
     </font>
     <font>
@@ -2679,50 +2617,20 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri Light"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Display"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri Light"/>
+      <name val="Aptos"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -2795,7 +2703,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2830,9 +2738,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2850,19 +2755,16 @@
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2871,49 +2773,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2922,6 +2792,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{1EB5855D-A8E9-42DE-A743-8C096ABB6D75}"/>
@@ -2959,7 +2847,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>years_dist!$B$19:$B$19</c:f>
+              <c:f>years_dist!$B$1:$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3031,7 +2919,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>years_dist!$A$20:$A$29</c:f>
+              <c:f>years_dist!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3070,7 +2958,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>years_dist!$B$20:$B$29</c:f>
+              <c:f>years_dist!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3112,7 +3000,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>years_dist!$C$19:$C$19</c:f>
+              <c:f>years_dist!$C$1:$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3184,7 +3072,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>years_dist!$A$20:$A$29</c:f>
+              <c:f>years_dist!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3223,7 +3111,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>years_dist!$C$20:$C$29</c:f>
+              <c:f>years_dist!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3275,7 +3163,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>years_dist!$D$19:$D$19</c:f>
+              <c:f>years_dist!$D$1:$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3347,7 +3235,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>years_dist!$A$20:$A$29</c:f>
+              <c:f>years_dist!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3386,7 +3274,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>years_dist!$D$20:$D$29</c:f>
+              <c:f>years_dist!$D$2:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3726,7 +3614,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>database_dist!$B$19:$B$19</c:f>
+              <c:f>database_dist!$B$10:$B$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3798,7 +3686,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>database_dist!$A$20:$A$27</c:f>
+              <c:f>database_dist!$A$11:$A$18</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3830,7 +3718,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>database_dist!$B$20:$B$27</c:f>
+              <c:f>database_dist!$B$11:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3869,7 +3757,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>database_dist!$C$19:$C$19</c:f>
+              <c:f>database_dist!$C$10:$C$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3941,7 +3829,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>database_dist!$A$20:$A$27</c:f>
+              <c:f>database_dist!$A$11:$A$18</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3973,7 +3861,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>database_dist!$C$20:$C$27</c:f>
+              <c:f>database_dist!$C$11:$C$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4016,7 +3904,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>database_dist!$D$19:$D$19</c:f>
+              <c:f>database_dist!$D$10:$D$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4119,7 +4007,7 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>database_dist!$A$20:$A$27</c:f>
+              <c:f>database_dist!$A$11:$A$18</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -4151,7 +4039,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>database_dist!$D$20:$D$27</c:f>
+              <c:f>database_dist!$D$11:$D$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4538,7 +4426,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>terms_dist!$B$15:$B$15</c:f>
+              <c:f>terms_dist!$B$1:$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4558,7 +4446,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>terms_dist!$A$16:$A$22</c:f>
+              <c:f>terms_dist!$A$2:$A$8</c:f>
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
@@ -4587,7 +4475,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>terms_dist!$B$16:$B$22</c:f>
+              <c:f>terms_dist!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5847,10 +5735,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>335283</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>15243</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>254003</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>63503</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3421383" cy="1691637"/>
     <xdr:graphicFrame macro="">
@@ -5883,10 +5771,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>497273</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>173362</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>397883</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>15772</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="3242129" cy="2066256"/>
     <xdr:graphicFrame macro="">
@@ -5919,10 +5807,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>146409</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>95429</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>38823</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>88898</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4572000" cy="2731770"/>
     <xdr:graphicFrame macro="">
@@ -7643,7 +7531,7 @@
     </row>
     <row r="17" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -7670,7 +7558,7 @@
     </row>
     <row r="18" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>459</v>
+        <v>408</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -7712,85 +7600,85 @@
   <sheetData>
     <row r="1" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>389</v>
+        <v>338</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>350</v>
+        <v>299</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>361</v>
+        <v>310</v>
       </c>
       <c r="H1" t="s">
-        <v>390</v>
+        <v>339</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>372</v>
+        <v>321</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
-        <v>391</v>
-      </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
+      <c r="A2" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
     </row>
     <row r="3" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>352</v>
+        <v>301</v>
       </c>
       <c r="C3" s="1">
         <v>2022</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>359</v>
+        <v>303</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>308</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>356</v>
+        <v>305</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>393</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7798,31 +7686,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>355</v>
+        <v>304</v>
       </c>
       <c r="C4" s="1">
         <v>2017</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>360</v>
+        <v>309</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>358</v>
+        <v>307</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>365</v>
+        <v>314</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7830,34 +7718,34 @@
         <v>21</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>395</v>
+        <v>344</v>
       </c>
       <c r="C5" s="1">
         <v>2019</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>363</v>
+        <v>312</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>366</v>
+        <v>315</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>394</v>
+        <v>343</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="K5" t="s">
-        <v>393</v>
+        <v>342</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7865,66 +7753,66 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="C6" s="1">
         <v>2017</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>396</v>
+        <v>303</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>345</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>369</v>
+        <v>318</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>397</v>
+        <v>346</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>367</v>
+        <v>316</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>398</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="C7" s="1">
         <v>2015</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>370</v>
+        <v>319</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>371</v>
+        <v>320</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>373</v>
+        <v>322</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="K7" t="s">
-        <v>399</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7932,28 +7820,28 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>376</v>
+        <v>325</v>
       </c>
       <c r="C8" s="1">
         <v>2007</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="E8" t="s">
-        <v>375</v>
+        <v>324</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>374</v>
+        <v>323</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>386</v>
+        <v>335</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="K8" t="s">
-        <v>400</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7965,338 +7853,338 @@
         <v>2018</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>377</v>
+        <v>326</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>378</v>
+        <v>327</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>401</v>
+        <v>350</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="K9" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" s="47" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="47" t="s">
-        <v>403</v>
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" s="33" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="33" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1">
         <v>2021</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>381</v>
+        <v>330</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>383</v>
+        <v>332</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>382</v>
+        <v>331</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>384</v>
+        <v>333</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>353</v>
+        <v>302</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>405</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>520</v>
+        <v>463</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1">
         <v>2018</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>406</v>
+        <v>330</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>355</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>407</v>
+        <v>356</v>
       </c>
       <c r="G12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>387</v>
+        <v>336</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="K12" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" s="46" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46" t="s">
-        <v>409</v>
+        <v>357</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" s="32" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="32" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>393</v>
+        <v>342</v>
       </c>
       <c r="C14" s="1">
         <v>2023</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="E14" t="s">
-        <v>410</v>
+        <v>359</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>357</v>
+        <v>306</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>411</v>
+        <v>360</v>
       </c>
       <c r="C15" s="1">
         <v>2016</v>
       </c>
       <c r="D15" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="E15" t="s">
-        <v>412</v>
+        <v>361</v>
       </c>
       <c r="F15" t="s">
-        <v>413</v>
+        <v>362</v>
       </c>
       <c r="G15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>371</v>
+        <v>320</v>
       </c>
       <c r="J15" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>415</v>
+        <v>364</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>416</v>
+        <v>365</v>
       </c>
       <c r="C16" s="1">
         <v>2022</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>417</v>
+      <c r="D16" s="22" t="s">
+        <v>366</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>418</v>
+        <v>367</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>419</v>
+        <v>368</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>371</v>
+        <v>320</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>420</v>
+        <v>369</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>422</v>
+        <v>370</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>371</v>
       </c>
       <c r="C17" s="1">
         <v>2024</v>
       </c>
-      <c r="D17" s="24" t="s">
-        <v>354</v>
+      <c r="D17" s="22" t="s">
+        <v>303</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>423</v>
+        <v>372</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>424</v>
+        <v>373</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>425</v>
+        <v>374</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="B18" s="25"/>
+        <v>349</v>
+      </c>
+      <c r="B18" s="23"/>
       <c r="C18" s="1">
         <v>2018</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="E18" t="s">
-        <v>426</v>
+        <v>375</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>427</v>
+        <v>376</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>428</v>
+        <v>377</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="1" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>429</v>
+        <v>378</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>430</v>
+        <v>379</v>
       </c>
       <c r="C19" s="1">
         <v>2024</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="E19" t="s">
-        <v>431</v>
+        <v>380</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>432</v>
+        <v>381</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>433</v>
+        <v>382</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>434</v>
+        <v>383</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>362</v>
+        <v>311</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
       <c r="C20" s="1">
         <v>2017</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>436</v>
+        <v>385</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>437</v>
+        <v>386</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>438</v>
+        <v>387</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
-        <v>414</v>
+        <v>363</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="C21" s="1">
         <v>2024</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>354</v>
+        <v>303</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>440</v>
+        <v>389</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>441</v>
+        <v>390</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>442</v>
+        <v>391</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>443</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -8333,25 +8221,25 @@
     <row r="1" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="J1" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>460</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>516</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>499</v>
+        <v>448</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>32</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>498</v>
+        <v>447</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>33</v>
@@ -8378,68 +8266,68 @@
     <row r="2" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="J2" s="11" t="s">
-        <v>472</v>
+        <v>421</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N2" s="11" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>500</v>
+        <v>449</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>100</v>
       </c>
       <c r="R2" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="S2" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="S2" s="11" t="s">
+      <c r="T2" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="T2" s="11" t="s">
+      <c r="U2" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="U2" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="V2" s="11" t="s">
         <v>46</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>477</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="J3" s="11" t="s">
-        <v>465</v>
+        <v>414</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="M3" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>66</v>
@@ -8460,7 +8348,7 @@
         <v>46</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>478</v>
+        <v>427</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -8469,25 +8357,25 @@
     <row r="4" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="J4" s="11" t="s">
-        <v>461</v>
+        <v>410</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>300</v>
+        <v>269</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>501</v>
+        <v>450</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>49</v>
@@ -8507,8 +8395,8 @@
       <c r="V4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="W4" s="27" t="s">
-        <v>479</v>
+      <c r="W4" s="25" t="s">
+        <v>428</v>
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -8517,25 +8405,25 @@
     <row r="5" spans="1:26" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="J5" s="11" t="s">
-        <v>470</v>
+        <v>419</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>502</v>
+        <v>451</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>93</v>
@@ -8555,8 +8443,8 @@
       <c r="V5" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="W5" s="27" t="s">
-        <v>480</v>
+      <c r="W5" s="25" t="s">
+        <v>429</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -8565,46 +8453,46 @@
     <row r="6" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="J6" s="11" t="s">
-        <v>476</v>
+        <v>425</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>500</v>
+        <v>449</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q6" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="R6" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="R6" s="11" t="s">
+      <c r="S6" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="S6" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="T6" s="11" t="s">
         <v>44</v>
       </c>
       <c r="U6" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="V6" s="11" t="s">
         <v>46</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>481</v>
+        <v>430</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -8613,25 +8501,25 @@
     <row r="7" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="J7" s="11" t="s">
-        <v>462</v>
+        <v>411</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O7" s="11" t="s">
-        <v>500</v>
+        <v>449</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>518</v>
+        <v>461</v>
       </c>
       <c r="Q7" s="11" t="s">
         <v>41</v>
@@ -8651,56 +8539,56 @@
       <c r="V7" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="W7" s="26" t="s">
-        <v>482</v>
+      <c r="W7" s="24" t="s">
+        <v>431</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="144" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="J8" s="11" t="s">
-        <v>475</v>
+        <v>424</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="N8" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="R8" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="R8" s="11" t="s">
+      <c r="S8" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="S8" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="T8" s="11" t="s">
         <v>75</v>
       </c>
       <c r="U8" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V8" s="11" t="s">
         <v>77</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>483</v>
+        <v>432</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -8709,25 +8597,25 @@
     <row r="9" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="J9" s="11" t="s">
-        <v>466</v>
+        <v>415</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>99</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q9" s="11" t="s">
         <v>72</v>
@@ -8735,7 +8623,7 @@
       <c r="R9" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="S9" s="28" t="s">
+      <c r="S9" s="26" t="s">
         <v>74</v>
       </c>
       <c r="T9" s="11" t="s">
@@ -8748,7 +8636,7 @@
         <v>77</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
@@ -8757,59 +8645,59 @@
     <row r="10" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="J10" s="11" t="s">
-        <v>471</v>
-      </c>
-      <c r="K10" s="28" t="s">
-        <v>221</v>
+        <v>420</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>216</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>497</v>
+        <v>446</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="N10" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="O10" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="P10" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="28"/>
-      <c r="S10" s="28"/>
-      <c r="T10" s="28"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
+        <v>229</v>
+      </c>
+      <c r="N10" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="O10" s="26" t="s">
+        <v>453</v>
+      </c>
+      <c r="P10" s="26" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q10" s="26"/>
+      <c r="R10" s="26"/>
+      <c r="S10" s="26"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="26"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="26"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="J11" s="11" t="s">
-        <v>467</v>
+        <v>416</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>496</v>
+        <v>445</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="O11" s="11" t="s">
-        <v>503</v>
+        <v>452</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>79</v>
@@ -8829,7 +8717,7 @@
       <c r="V11" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="W11" s="26" t="s">
+      <c r="W11" s="24" t="s">
         <v>83</v>
       </c>
       <c r="X11" s="1"/>
@@ -8838,46 +8726,46 @@
     </row>
     <row r="12" spans="1:26" ht="331.2" x14ac:dyDescent="0.3">
       <c r="J12" s="11" t="s">
-        <v>474</v>
+        <v>423</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>495</v>
+        <v>444</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="O12" s="11" t="s">
-        <v>502</v>
+        <v>451</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="Q12" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="R12" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="R12" s="11" t="s">
+      <c r="S12" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="T12" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="T12" s="28" t="s">
+      <c r="U12" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="U12" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="V12" s="11" t="s">
         <v>46</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>485</v>
+        <v>434</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -8887,70 +8775,70 @@
       <c r="A13" s="6"/>
       <c r="I13" s="10"/>
       <c r="J13" s="11" t="s">
-        <v>469</v>
+        <v>418</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>494</v>
+        <v>443</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>505</v>
+        <v>454</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="Q13" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="R13" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="R13" s="11" t="s">
+      <c r="S13" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="S13" s="11" t="s">
-        <v>130</v>
       </c>
       <c r="T13" s="11" t="s">
         <v>57</v>
       </c>
       <c r="U13" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="V13" s="11" t="s">
         <v>77</v>
       </c>
       <c r="W13" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="J14" s="11" t="s">
-        <v>464</v>
+        <v>413</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>299</v>
+        <v>268</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>502</v>
+        <v>451</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="Q14" s="11" t="s">
         <v>54</v>
@@ -8971,7 +8859,7 @@
         <v>46</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>486</v>
+        <v>435</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -8980,25 +8868,25 @@
     <row r="15" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="J15" s="11" t="s">
-        <v>463</v>
+        <v>412</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>493</v>
+        <v>442</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="O15" s="11" t="s">
-        <v>506</v>
+        <v>455</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="Q15" s="11" t="s">
         <v>60</v>
@@ -9019,7 +8907,7 @@
         <v>46</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>487</v>
+        <v>436</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -9028,73 +8916,73 @@
     <row r="16" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="J16" s="11" t="s">
-        <v>473</v>
-      </c>
-      <c r="K16" s="28" t="s">
-        <v>221</v>
-      </c>
-      <c r="L16" s="28" t="s">
-        <v>492</v>
+        <v>422</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>216</v>
+      </c>
+      <c r="L16" s="26" t="s">
+        <v>441</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>236</v>
-      </c>
-      <c r="N16" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="O16" s="28" t="s">
-        <v>502</v>
-      </c>
-      <c r="P16" s="28" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q16" s="28" t="s">
+        <v>227</v>
+      </c>
+      <c r="N16" s="26" t="s">
+        <v>220</v>
+      </c>
+      <c r="O16" s="26" t="s">
+        <v>451</v>
+      </c>
+      <c r="P16" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q16" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="R16" s="11" t="s">
+        <v>462</v>
+      </c>
+      <c r="S16" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="R16" s="11" t="s">
-        <v>519</v>
-      </c>
-      <c r="S16" s="28" t="s">
+      <c r="T16" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="T16" s="11" t="s">
+      <c r="U16" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="U16" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="V16" s="11" t="s">
         <v>77</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>488</v>
+        <v>437</v>
       </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="216" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="J17" s="11" t="s">
-        <v>468</v>
+        <v>417</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>490</v>
+        <v>439</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>491</v>
+        <v>440</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>302</v>
+        <v>271</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>507</v>
+        <v>456</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>86</v>
@@ -9115,7 +9003,7 @@
         <v>91</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>489</v>
+        <v>438</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -9500,192 +9388,192 @@
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="3" width="11.5546875" customWidth="1"/>
     <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="1"/>
+    <col min="5" max="5" width="19" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B1" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C1" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="F1" t="s">
         <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="144" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>261</v>
+        <v>466</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
-        <v>246</v>
+        <v>465</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="193.8" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="E3" s="22" t="s">
-        <v>250</v>
+        <v>467</v>
+      </c>
+      <c r="E3" s="34" t="s">
+        <v>236</v>
       </c>
       <c r="F3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
-        <v>249</v>
+        <v>468</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="1" t="s">
-        <v>248</v>
+        <v>469</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>259</v>
+      <c r="A6" s="1" t="s">
+        <v>467</v>
       </c>
       <c r="B6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>255</v>
+        <v>240</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>241</v>
       </c>
       <c r="E6" s="1">
         <v>0.6</v>
       </c>
       <c r="F6" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>260</v>
+        <v>472</v>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>263</v>
+        <v>240</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>245</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="F7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>258</v>
+        <v>474</v>
       </c>
       <c r="B8" t="s">
-        <v>291</v>
+        <v>261</v>
       </c>
       <c r="C8" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>262</v>
+        <v>244</v>
       </c>
       <c r="F8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>248</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>469</v>
       </c>
       <c r="B9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>255</v>
+        <v>240</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>241</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="F9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G9" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
-      <c r="D10" t="s">
-        <v>265</v>
+      <c r="D10" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>267</v>
+        <v>480</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>263</v>
+        <v>240</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>245</v>
       </c>
       <c r="E11" s="1">
         <v>0.31</v>
       </c>
       <c r="F11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>268</v>
+        <v>471</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>255</v>
+        <v>240</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>241</v>
       </c>
       <c r="E12" s="1">
         <v>0.60560000000000003</v>
@@ -9693,202 +9581,193 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>269</v>
+        <v>479</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>255</v>
+        <v>240</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>241</v>
       </c>
       <c r="E13" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
-      <c r="C14" s="21"/>
+      <c r="C14" s="20"/>
       <c r="D14" t="s">
-        <v>271</v>
+        <v>470</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>274</v>
+        <v>478</v>
       </c>
       <c r="B15" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="C15" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="F15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>270</v>
+        <v>477</v>
       </c>
       <c r="B16" t="s">
-        <v>254</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>255</v>
+        <v>240</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>241</v>
       </c>
       <c r="E16" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F16" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
-      <c r="C17" s="21"/>
+      <c r="C17" s="20"/>
       <c r="D17" t="s">
-        <v>271</v>
+        <v>470</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>265</v>
+        <v>248</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>468</v>
       </c>
       <c r="B18" t="s">
-        <v>290</v>
+        <v>260</v>
       </c>
       <c r="C18" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="F18" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>277</v>
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
+        <v>476</v>
       </c>
       <c r="B19" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C19" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
       <c r="F19" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>279</v>
+        <v>473</v>
       </c>
       <c r="B20" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C20" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="F20" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D21" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B22" t="s">
+        <v>256</v>
+      </c>
+      <c r="C22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E21" s="1" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="B22" t="s">
-        <v>284</v>
-      </c>
-      <c r="C22" t="s">
-        <v>286</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>287</v>
-      </c>
       <c r="F22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>288</v>
+        <v>482</v>
       </c>
       <c r="B23" t="s">
-        <v>289</v>
+        <v>259</v>
       </c>
       <c r="C23" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="E23" s="1">
         <v>94.3</v>
       </c>
       <c r="F23" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>292</v>
+        <v>483</v>
       </c>
       <c r="B24" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="C24" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="F24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" xr:uid="{E63F0AE2-EC32-475A-9207-B0A8CC6E4BB4}"/>
-    <hyperlink ref="C7" r:id="rId2" xr:uid="{510EA5E7-5C8D-4471-B5A7-F77073E2419F}"/>
-    <hyperlink ref="C9" r:id="rId3" xr:uid="{0AAAF3A2-25A2-4ECB-92AD-E3D69CB7194F}"/>
-    <hyperlink ref="C11" r:id="rId4" xr:uid="{1FD1CA34-D969-4AEB-ABAD-D72EB7305392}"/>
-    <hyperlink ref="C12" r:id="rId5" xr:uid="{2E260BDB-1FE0-4936-AF83-0C4D32C8F76E}"/>
-    <hyperlink ref="C13" r:id="rId6" xr:uid="{4DCA0CDB-ACB0-4E1D-8F78-8E0EF644C408}"/>
-    <hyperlink ref="C16" r:id="rId7" xr:uid="{BF75BC25-035E-4E5C-A3FA-7AAE4FDA6D46}"/>
-  </hyperlinks>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9896,7 +9775,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399DB999-9283-4751-BBD0-238C098D8C5B}">
   <sheetPr codeName="Sheet7"/>
-  <dimension ref="A19:D30"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -9919,153 +9798,153 @@
     <col min="26" max="26" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>133</v>
-      </c>
-      <c r="B19" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" t="s">
         <v>137</v>
       </c>
-      <c r="C19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="D1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>2015</v>
       </c>
-      <c r="C20">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="D20">
+      <c r="D2">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3">
         <v>2016</v>
       </c>
-      <c r="B21">
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="D21">
+      <c r="D3">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4">
         <v>2017</v>
       </c>
-      <c r="B22">
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="C22">
+      <c r="C4">
         <v>2</v>
       </c>
-      <c r="D22">
+      <c r="D4">
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5">
         <v>2018</v>
       </c>
-      <c r="B23">
+      <c r="B5">
         <v>1</v>
       </c>
-      <c r="C23">
+      <c r="C5">
         <v>1</v>
       </c>
-      <c r="D23">
+      <c r="D5">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6">
         <v>2019</v>
       </c>
-      <c r="C24">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D24">
+      <c r="D6">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7">
         <v>2021</v>
       </c>
-      <c r="B25">
+      <c r="B7">
         <v>3</v>
       </c>
-      <c r="D25">
+      <c r="D7">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>2022</v>
       </c>
-      <c r="B26">
+      <c r="B8">
         <v>1</v>
       </c>
-      <c r="C26">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D26">
+      <c r="D8">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9">
         <v>2023</v>
       </c>
-      <c r="B27">
+      <c r="B9">
         <v>3</v>
       </c>
-      <c r="D27">
+      <c r="D9">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10">
         <v>2024</v>
       </c>
-      <c r="B28">
+      <c r="B10">
         <v>4</v>
       </c>
-      <c r="D28">
+      <c r="D10">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11">
         <v>2025</v>
       </c>
-      <c r="B29">
+      <c r="B11">
         <v>2</v>
       </c>
-      <c r="C29">
+      <c r="C11">
         <v>1</v>
       </c>
-      <c r="D29">
+      <c r="D11">
         <v>3</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>136</v>
-      </c>
-      <c r="B30">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>135</v>
+      </c>
+      <c r="B12">
         <v>16</v>
       </c>
-      <c r="C30">
+      <c r="C12">
         <v>7</v>
       </c>
-      <c r="D30">
+      <c r="D12">
         <v>23</v>
       </c>
     </row>
@@ -10078,7 +9957,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F8EC5-B561-4123-A5F6-54D916B5F663}">
   <sheetPr codeName="Sheet8"/>
-  <dimension ref="A19:D27"/>
+  <dimension ref="A10:D18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.88671875" bestFit="1" customWidth="1"/>
@@ -10088,108 +9967,108 @@
     <col min="5" max="5" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" t="s">
         <v>137</v>
       </c>
-      <c r="C19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="D10" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>139</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>140</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>142</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>145</v>
       </c>
-      <c r="B20">
+      <c r="B16">
+        <v>3</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17">
         <v>1</v>
       </c>
-      <c r="D20">
+      <c r="C17">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
+      <c r="D17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18">
         <v>3</v>
       </c>
-      <c r="D21">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>141</v>
-      </c>
-      <c r="B22">
-        <v>5</v>
-      </c>
-      <c r="D22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>144</v>
-      </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-      <c r="D26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>147</v>
-      </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27">
+      <c r="D18">
         <v>3</v>
       </c>
     </row>
@@ -10202,7 +10081,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA0438A-EE17-4255-B1AE-346A842E6C2A}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A15:B22"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -10210,67 +10089,67 @@
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="B15" s="16" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B16" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B17" s="17">
+      <c r="B5" s="16">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="B19" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" s="17">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B6" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="17">
+      <c r="B7" s="16">
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="17">
+      <c r="B8" s="16">
         <v>4</v>
       </c>
     </row>
@@ -10292,29 +10171,29 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>508</v>
+        <v>457</v>
       </c>
       <c r="B1" t="s">
-        <v>509</v>
+        <v>458</v>
       </c>
       <c r="C1" t="s">
-        <v>510</v>
+        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>75</v>
@@ -10322,18 +10201,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>189</v>
+        <v>485</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -10341,7 +10220,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>75</v>
@@ -10349,29 +10228,29 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>44</v>
@@ -10379,10 +10258,10 @@
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
@@ -10390,76 +10269,76 @@
     </row>
     <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
@@ -10488,43 +10367,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10532,33 +10411,33 @@
         <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G2" s="1">
         <v>2025</v>
       </c>
-      <c r="H2" s="18">
+      <c r="H2" s="17">
         <v>45870</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10566,33 +10445,33 @@
         <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G3" s="1">
         <v>2023</v>
       </c>
-      <c r="H3" s="18">
+      <c r="H3" s="17">
         <v>45108</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10600,33 +10479,33 @@
         <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G4" s="1">
         <v>2022</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="17">
         <v>44593</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>449</v>
+        <v>398</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10634,33 +10513,33 @@
         <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="F5" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="G5" s="19">
+      <c r="F5" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="G5" s="18">
         <v>2025</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="17">
         <v>45839</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10668,33 +10547,33 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G6" s="1">
         <v>2024</v>
       </c>
-      <c r="H6" s="18">
+      <c r="H6" s="17">
         <v>45413</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10702,33 +10581,33 @@
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
-      <c r="F7" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="G7" s="19">
+      <c r="F7" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="G7" s="18">
         <v>2021</v>
       </c>
-      <c r="H7" s="18">
+      <c r="H7" s="17">
         <v>44197</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10738,97 +10617,97 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G8" s="1">
         <v>2024</v>
       </c>
-      <c r="H8" s="18">
+      <c r="H8" s="17">
         <v>45352</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>451</v>
+        <v>400</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G9" s="1">
         <v>2016</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <v>42614</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G10" s="1">
         <v>2021</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <v>44317</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10836,101 +10715,101 @@
         <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G11" s="1">
         <v>2023</v>
       </c>
-      <c r="H11" s="18">
+      <c r="H11" s="17">
         <v>45139</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>450</v>
+        <v>399</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G12" s="1">
         <v>2017</v>
       </c>
-      <c r="H12" s="18">
+      <c r="H12" s="17">
         <v>42856</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="45" t="s">
-        <v>127</v>
+      <c r="A13" s="31" t="s">
+        <v>126</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G13" s="1">
         <v>2024</v>
       </c>
-      <c r="H13" s="18">
+      <c r="H13" s="17">
         <v>45383</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>457</v>
+        <v>406</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10938,67 +10817,67 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G14" s="1">
         <v>2023</v>
       </c>
-      <c r="H14" s="18">
+      <c r="H14" s="17">
         <v>45108</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>456</v>
+        <v>405</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>453</v>
+        <v>402</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G15" s="1">
         <v>2018</v>
       </c>
-      <c r="H15" s="18">
+      <c r="H15" s="17">
         <v>43313</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>455</v>
+        <v>404</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -11007,64 +10886,64 @@
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G16" s="1">
         <v>2024</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="17">
         <v>45413</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B17" t="s">
-        <v>158</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="G17" s="1">
         <v>2021</v>
       </c>
-      <c r="H17" s="20">
+      <c r="H17" s="19">
         <v>44378</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
@@ -11072,31 +10951,31 @@
         <v>3</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G18" s="1">
         <v>2017</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="19">
         <v>42826</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -11104,31 +10983,31 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G19" s="1">
         <v>2019</v>
       </c>
-      <c r="H19" s="20">
+      <c r="H19" s="19">
         <v>43617</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -11136,31 +11015,31 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G20" s="1">
         <v>2017</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="17">
         <v>42979</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>444</v>
+        <v>393</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
@@ -11168,54 +11047,54 @@
         <v>11</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G21" s="1">
         <v>2022</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="19">
         <v>44743</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>445</v>
+        <v>394</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G22" s="1">
         <v>2015</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="19">
         <v>43101</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>447</v>
+        <v>396</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
@@ -11223,7 +11102,7 @@
         <v>9</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F23"/>
       <c r="G23" s="1">
@@ -11233,13 +11112,13 @@
         <v>2007</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>448</v>
+        <v>397</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
@@ -11247,27 +11126,27 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G24" s="1">
         <v>2018</v>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="19">
         <v>43101</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L24" t="s">
-        <v>446</v>
+        <v>395</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
-      <c r="H25" s="20"/>
+      <c r="H25" s="19"/>
       <c r="K25" s="1"/>
       <c r="M25" s="1"/>
     </row>
@@ -11276,7 +11155,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
-      <c r="E27" s="23"/>
+      <c r="E27" s="21"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="K27" s="1"/>
@@ -11303,7 +11182,7 @@
       <c r="B30" s="2"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="23"/>
+      <c r="E30" s="21"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="K30" s="1"/>
@@ -11346,839 +11225,621 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A374C9BF-BD00-4473-A5C0-F0EEC750D063}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="E1:T39"/>
+  <dimension ref="E1:Q39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="29.77734375" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:20" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E1" s="29" t="s">
+    <row r="1" spans="5:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E1" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="29" t="s">
-        <v>516</v>
-      </c>
-      <c r="G1" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="H1" s="29" t="s">
-        <v>517</v>
-      </c>
-      <c r="I1" s="29" t="s">
+      <c r="F1" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="J1" s="29" t="s">
-        <v>298</v>
-      </c>
-      <c r="K1" s="30" t="s">
+      <c r="G1" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="H1" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="29" t="s">
-        <v>319</v>
-      </c>
-      <c r="N1" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="O1" s="32" t="s">
-        <v>324</v>
-      </c>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-    </row>
-    <row r="2" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E2" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>228</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I2" s="33" t="s">
+      <c r="I1" s="41"/>
+      <c r="J1" s="27" t="s">
+        <v>497</v>
+      </c>
+      <c r="K1" s="27" t="s">
+        <v>274</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>279</v>
+      </c>
+      <c r="M1" s="30"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+    </row>
+    <row r="2" spans="5:17" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="E2" s="37" t="s">
+        <v>486</v>
+      </c>
+      <c r="F2" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="K2" s="33" t="s">
+      <c r="G2" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="H2" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="31"/>
-      <c r="M2" s="33" t="s">
-        <v>511</v>
-      </c>
-      <c r="N2" s="34" t="s">
-        <v>327</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>521</v>
-      </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-    </row>
-    <row r="3" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E3" s="33" t="s">
-        <v>304</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>217</v>
-      </c>
-      <c r="G3" s="33" t="s">
+      <c r="I2" s="38"/>
+      <c r="J2" s="37" t="s">
+        <v>499</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>498</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>464</v>
+      </c>
+      <c r="M2" s="30"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+    </row>
+    <row r="3" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="E3" s="37" t="s">
+        <v>487</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I3" s="38"/>
+      <c r="J3" s="39" t="s">
+        <v>500</v>
+      </c>
+      <c r="K3" s="39" t="s">
+        <v>501</v>
+      </c>
+      <c r="L3" s="39" t="s">
+        <v>278</v>
+      </c>
+      <c r="M3" s="30"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+    </row>
+    <row r="4" spans="5:17" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="E4" s="37" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="38"/>
+      <c r="J4" s="39" t="s">
+        <v>502</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>503</v>
+      </c>
+      <c r="L4" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="M4" s="30"/>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+    </row>
+    <row r="5" spans="5:17" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="E5" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="H5" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="38"/>
+      <c r="J5" s="39" t="s">
+        <v>504</v>
+      </c>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39" t="s">
+        <v>249</v>
+      </c>
+      <c r="M5" s="30"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+    </row>
+    <row r="6" spans="5:17" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="E6" s="37" t="s">
+        <v>202</v>
+      </c>
+      <c r="F6" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="H6" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="38"/>
+      <c r="J6" s="39" t="s">
+        <v>506</v>
+      </c>
+      <c r="K6" s="39" t="s">
+        <v>505</v>
+      </c>
+      <c r="L6" s="39" t="s">
+        <v>289</v>
+      </c>
+      <c r="M6" s="30"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="29"/>
+    </row>
+    <row r="7" spans="5:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E7" s="37" t="s">
+        <v>195</v>
+      </c>
+      <c r="F7" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>461</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="38"/>
+      <c r="J7" s="39" t="s">
+        <v>507</v>
+      </c>
+      <c r="K7" s="39" t="s">
+        <v>506</v>
+      </c>
+      <c r="L7" s="39" t="s">
+        <v>290</v>
+      </c>
+      <c r="M7" s="30"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="29"/>
+    </row>
+    <row r="8" spans="5:17" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="E8" s="37" t="s">
+        <v>488</v>
+      </c>
+      <c r="F8" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>240</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="38"/>
+      <c r="J8" s="39" t="s">
+        <v>276</v>
+      </c>
+      <c r="K8" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="L8" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="M8" s="30"/>
+      <c r="N8" s="29"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29"/>
+    </row>
+    <row r="9" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="E9" s="37" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="38"/>
+      <c r="J9" s="39" t="s">
+        <v>281</v>
+      </c>
+      <c r="K9" s="39" t="s">
+        <v>284</v>
+      </c>
+      <c r="L9" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="M9" s="30"/>
+      <c r="N9" s="29"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="29"/>
+    </row>
+    <row r="10" spans="5:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="E10" s="40" t="s">
+        <v>489</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="G10" s="40" t="s">
+        <v>264</v>
+      </c>
+      <c r="H10" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="39" t="s">
+        <v>508</v>
+      </c>
+      <c r="M10" s="30"/>
+      <c r="N10" s="29"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="29"/>
+    </row>
+    <row r="11" spans="5:17" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="E11" s="37" t="s">
+        <v>197</v>
+      </c>
+      <c r="F11" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="H3" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I3" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="J3" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="K3" s="33" t="s">
+      <c r="G11" s="37" t="s">
+        <v>277</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="38"/>
+      <c r="J11" s="39" t="s">
+        <v>282</v>
+      </c>
+      <c r="K11" s="39" t="s">
+        <v>283</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>292</v>
+      </c>
+      <c r="M11" s="30"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+    </row>
+    <row r="12" spans="5:17" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="E12" s="37" t="s">
+        <v>490</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>224</v>
+      </c>
+      <c r="G12" s="37" t="s">
+        <v>265</v>
+      </c>
+      <c r="H12" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="31"/>
-      <c r="M3" s="32" t="s">
-        <v>512</v>
-      </c>
-      <c r="N3" s="32" t="s">
-        <v>328</v>
-      </c>
-      <c r="O3" s="35" t="s">
-        <v>323</v>
-      </c>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="31"/>
-      <c r="S3" s="31"/>
-      <c r="T3" s="31"/>
-    </row>
-    <row r="4" spans="5:20" ht="156.6" x14ac:dyDescent="0.3">
-      <c r="E4" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="F4" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="G4" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="K4" s="33" t="s">
+      <c r="I12" s="38"/>
+      <c r="J12" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="K12" s="39" t="s">
+        <v>496</v>
+      </c>
+      <c r="L12" s="39"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="29"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="29"/>
+    </row>
+    <row r="13" spans="5:17" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="E13" s="37" t="s">
+        <v>200</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="G13" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I13" s="38"/>
+      <c r="J13" s="39" t="s">
+        <v>493</v>
+      </c>
+      <c r="K13" s="39" t="s">
+        <v>494</v>
+      </c>
+      <c r="L13" s="39" t="s">
+        <v>493</v>
+      </c>
+      <c r="M13" s="30"/>
+      <c r="N13" s="29"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="29"/>
+    </row>
+    <row r="14" spans="5:17" ht="216" x14ac:dyDescent="0.3">
+      <c r="E14" s="37" t="s">
+        <v>491</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>268</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>266</v>
+      </c>
+      <c r="H14" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="31"/>
-      <c r="M4" s="36" t="s">
-        <v>513</v>
-      </c>
-      <c r="N4" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="O4" s="32" t="s">
-        <v>340</v>
-      </c>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="5:20" ht="96.6" x14ac:dyDescent="0.3">
-      <c r="E5" s="33" t="s">
-        <v>282</v>
-      </c>
-      <c r="F5" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="G5" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="K5" s="33" t="s">
+      <c r="I14" s="38"/>
+      <c r="J14" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="K14" s="39" t="s">
+        <v>337</v>
+      </c>
+      <c r="L14" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="M14" s="30"/>
+      <c r="N14" s="29"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+    </row>
+    <row r="15" spans="5:17" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="E15" s="37" t="s">
+        <v>492</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="H15" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="31"/>
-      <c r="M5" s="36" t="s">
-        <v>514</v>
-      </c>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32" t="s">
+      <c r="I15" s="38"/>
+      <c r="J15" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="K15" s="39"/>
+      <c r="L15" s="39" t="s">
+        <v>293</v>
+      </c>
+      <c r="M15" s="30"/>
+      <c r="N15" s="29"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+    </row>
+    <row r="16" spans="5:17" ht="72" x14ac:dyDescent="0.3">
+      <c r="E16" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="H16" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-    </row>
-    <row r="6" spans="5:20" ht="288" x14ac:dyDescent="0.3">
-      <c r="E6" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="H6" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="J6" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="K6" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="31"/>
-      <c r="M6" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="N6" s="32" t="s">
-        <v>329</v>
-      </c>
-      <c r="O6" s="32" t="s">
-        <v>340</v>
-      </c>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-    </row>
-    <row r="7" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E7" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="I7" s="33" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" s="33" t="s">
-        <v>515</v>
-      </c>
-      <c r="K7" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="L7" s="31"/>
-      <c r="M7" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="O7" s="32" t="s">
-        <v>341</v>
-      </c>
-      <c r="P7" s="32"/>
-      <c r="Q7" s="31"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="31"/>
-      <c r="T7" s="31"/>
-    </row>
-    <row r="8" spans="5:20" ht="79.8" x14ac:dyDescent="0.3">
-      <c r="E8" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="G8" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="J8" s="29" t="s">
-        <v>254</v>
-      </c>
-      <c r="K8" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="L8" s="31"/>
-      <c r="M8" s="38" t="s">
-        <v>321</v>
-      </c>
-      <c r="N8" s="38" t="s">
-        <v>320</v>
-      </c>
-      <c r="O8" s="32" t="s">
-        <v>342</v>
-      </c>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="31"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="31"/>
-      <c r="T8" s="31"/>
-    </row>
-    <row r="9" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="E9" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>225</v>
-      </c>
-      <c r="G9" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="H9" s="33" t="s">
+      <c r="I16" s="38"/>
+      <c r="J16" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="K16" s="39" t="s">
+        <v>288</v>
+      </c>
+      <c r="L16" s="39"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="29"/>
+    </row>
+    <row r="17" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="E17" s="37" t="s">
+        <v>207</v>
+      </c>
+      <c r="F17" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="I9" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="J9" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="K9" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32" t="s">
-        <v>330</v>
-      </c>
-      <c r="N9" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="O9" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="31"/>
-    </row>
-    <row r="10" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E10" s="40" t="s">
-        <v>310</v>
-      </c>
-      <c r="F10" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="G10" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="I10" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="J10" s="40" t="s">
-        <v>295</v>
-      </c>
-      <c r="K10" s="40" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="41"/>
-      <c r="O10" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-    </row>
-    <row r="11" spans="5:20" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="E11" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="F11" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>223</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="J11" s="33" t="s">
-        <v>322</v>
-      </c>
-      <c r="K11" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="N11" s="39" t="s">
-        <v>332</v>
-      </c>
-      <c r="O11" s="32" t="s">
-        <v>343</v>
-      </c>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="31"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="31"/>
-      <c r="T11" s="31"/>
-    </row>
-    <row r="12" spans="5:20" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E12" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="F12" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="G12" s="33" t="s">
-        <v>234</v>
-      </c>
-      <c r="H12" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="I12" s="33" t="s">
-        <v>231</v>
-      </c>
-      <c r="J12" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="K12" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="L12" s="31"/>
-      <c r="M12" s="33" t="s">
-        <v>334</v>
-      </c>
-      <c r="N12" s="32" t="s">
-        <v>335</v>
-      </c>
-      <c r="O12" s="32"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="31"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="31"/>
-      <c r="T12" s="31"/>
-    </row>
-    <row r="13" spans="5:20" ht="53.4" x14ac:dyDescent="0.3">
-      <c r="E13" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="F13" s="33" t="s">
-        <v>210</v>
-      </c>
-      <c r="G13" s="33" t="s">
-        <v>213</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="I13" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="J13" s="33" t="s">
-        <v>241</v>
-      </c>
-      <c r="K13" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="L13" s="31"/>
-      <c r="M13" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="N13" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="O13" s="37" t="s">
-        <v>336</v>
-      </c>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-    </row>
-    <row r="14" spans="5:20" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="E14" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="33" t="s">
-        <v>214</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="J14" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="K14" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="L14" s="31"/>
-      <c r="M14" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="N14" s="32" t="s">
-        <v>388</v>
-      </c>
-      <c r="O14" s="37" t="s">
-        <v>325</v>
-      </c>
-      <c r="P14" s="32"/>
-      <c r="Q14" s="31"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="31"/>
-      <c r="T14" s="31"/>
-    </row>
-    <row r="15" spans="5:20" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="E15" s="33" t="s">
-        <v>314</v>
-      </c>
-      <c r="F15" s="33" t="s">
-        <v>240</v>
-      </c>
-      <c r="G15" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="I15" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="J15" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="K15" s="33" t="s">
-        <v>46</v>
-      </c>
-      <c r="L15" s="31"/>
-      <c r="M15" s="33" t="s">
-        <v>337</v>
-      </c>
-      <c r="N15" s="32"/>
-      <c r="O15" s="43" t="s">
-        <v>344</v>
-      </c>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="31"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="31"/>
-      <c r="T15" s="31"/>
-    </row>
-    <row r="16" spans="5:20" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E16" s="44" t="s">
-        <v>315</v>
-      </c>
-      <c r="F16" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="G16" s="40" t="s">
-        <v>218</v>
-      </c>
-      <c r="H16" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>226</v>
-      </c>
-      <c r="J16" s="40" t="s">
-        <v>289</v>
-      </c>
-      <c r="K16" s="33" t="s">
-        <v>317</v>
-      </c>
-      <c r="L16" s="31"/>
-      <c r="M16" s="32" t="s">
-        <v>338</v>
-      </c>
-      <c r="N16" s="32" t="s">
-        <v>339</v>
-      </c>
-      <c r="O16" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-    </row>
-    <row r="17" spans="5:20" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="E17" s="33" t="s">
-        <v>316</v>
-      </c>
-      <c r="F17" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="G17" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="H17" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>226</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="K17" s="33" t="s">
+      <c r="G17" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="H17" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="L17" s="31"/>
-      <c r="M17" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="N17" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="O17" s="32" t="s">
-        <v>326</v>
-      </c>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-    </row>
-    <row r="18" spans="5:20" x14ac:dyDescent="0.3">
+      <c r="I17" s="38"/>
+      <c r="J17" s="39" t="s">
+        <v>495</v>
+      </c>
+      <c r="K17" s="39" t="s">
+        <v>495</v>
+      </c>
+      <c r="L17" s="39" t="s">
+        <v>495</v>
+      </c>
+      <c r="M17" s="30"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="29"/>
+    </row>
+    <row r="18" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="1"/>
-    </row>
-    <row r="19" spans="5:20" x14ac:dyDescent="0.3">
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-    </row>
-    <row r="22" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
-      <c r="K22" s="5"/>
-    </row>
-    <row r="23" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="5"/>
-      <c r="J24" s="5"/>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-    </row>
-    <row r="26" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="5"/>
-      <c r="J26" s="5"/>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
-      <c r="K27" s="5"/>
-    </row>
-    <row r="28" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-    </row>
-    <row r="29" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
-      <c r="J29" s="5"/>
-      <c r="K29" s="5"/>
-    </row>
-    <row r="30" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-    </row>
-    <row r="31" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-    </row>
-    <row r="32" spans="5:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="5:17" x14ac:dyDescent="0.3">
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
-      <c r="I32" s="5"/>
-      <c r="J32" s="5"/>
-      <c r="K32" s="5"/>
-    </row>
-    <row r="33" spans="5:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-    </row>
-    <row r="34" spans="5:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5"/>
-      <c r="K34" s="5"/>
-    </row>
-    <row r="35" spans="5:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
-      <c r="J35" s="5"/>
-      <c r="K35" s="5"/>
-    </row>
-    <row r="36" spans="5:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
-      <c r="K36" s="5"/>
-    </row>
-    <row r="37" spans="5:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-    </row>
-    <row r="38" spans="5:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-    </row>
-    <row r="39" spans="5:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="5:8" x14ac:dyDescent="0.3">
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="5"/>
-      <c r="J39" s="5"/>
-      <c r="K39" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DarkJargon_SoK_taxonomy_tables.xlsx
+++ b/DarkJargon_SoK_taxonomy_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\Projekte\DarkJargon-SOK-USENIX26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniluxembourg-my.sharepoint.com/personal/laura_bernardy_uni_lu/Documents/Documents/GitHub/DarkJargon-SOK-USENIX26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889C5A6C-99FE-49D5-B057-CE0D9F29AF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{889C5A6C-99FE-49D5-B057-CE0D9F29AF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09900854-4285-4AAF-83CB-19AA28E01EAF}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21360" firstSheet="1" activeTab="8" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="4" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="511">
   <si>
     <t>Approaches</t>
   </si>
@@ -2535,6 +2535,12 @@
   </si>
   <si>
     <t>dataset m by yuan</t>
+  </si>
+  <si>
+    <t>Johannes Bogensperger, Sven Schlarb, Allan Hanbury, Gábor Recski. "DreamDrug - A crowdsourced NER dataset for detecting drugs in darknet markets." (2021)</t>
+  </si>
+  <si>
+    <t>Seventh Workshop on Noisy User-generated Text (W-NUT 2021)</t>
   </si>
 </sst>
 </file>
@@ -2703,7 +2709,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2786,16 +2792,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2810,6 +2809,12 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{1EB5855D-A8E9-42DE-A743-8C096ABB6D75}"/>
@@ -3127,6 +3132,9 @@
                 <c:pt idx="4">
                   <c:v>1</c:v>
                 </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
                 </c:pt>
@@ -3294,7 +3302,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>2</c:v>
@@ -3726,7 +3734,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -4047,7 +4055,7 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4</c:v>
+                  <c:v>5</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -7631,20 +7639,20 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="39" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -7877,8 +7885,8 @@
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="33" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33" t="s">
+    <row r="10" spans="1:12" s="40" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="40" t="s">
         <v>352</v>
       </c>
     </row>
@@ -7948,8 +7956,8 @@
         <v>357</v>
       </c>
     </row>
-    <row r="13" spans="1:12" s="32" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="32" t="s">
+    <row r="13" spans="1:12" s="39" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="39" t="s">
         <v>358</v>
       </c>
     </row>
@@ -9439,7 +9447,7 @@
       <c r="D3" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="E3" s="34" t="s">
+      <c r="E3" s="32" t="s">
         <v>236</v>
       </c>
       <c r="F3" s="2"/>
@@ -9475,7 +9483,7 @@
       <c r="B6" t="s">
         <v>240</v>
       </c>
-      <c r="C6" s="35" t="s">
+      <c r="C6" t="s">
         <v>241</v>
       </c>
       <c r="E6" s="1">
@@ -9492,7 +9500,7 @@
       <c r="B7" t="s">
         <v>240</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="C7" t="s">
         <v>245</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -9526,7 +9534,7 @@
       <c r="B9" t="s">
         <v>240</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" t="s">
         <v>241</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -9555,7 +9563,7 @@
       <c r="B11" t="s">
         <v>240</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" t="s">
         <v>245</v>
       </c>
       <c r="E11" s="1">
@@ -9572,7 +9580,7 @@
       <c r="B12" t="s">
         <v>240</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" t="s">
         <v>241</v>
       </c>
       <c r="E12" s="1">
@@ -9586,7 +9594,7 @@
       <c r="B13" t="s">
         <v>240</v>
       </c>
-      <c r="C13" s="35" t="s">
+      <c r="C13" t="s">
         <v>241</v>
       </c>
       <c r="E13" s="1">
@@ -9633,7 +9641,7 @@
       <c r="B16" t="s">
         <v>240</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" t="s">
         <v>241</v>
       </c>
       <c r="E16" s="1">
@@ -9671,7 +9679,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="33" t="s">
         <v>476</v>
       </c>
       <c r="B19" t="s">
@@ -9880,8 +9888,11 @@
       <c r="B7">
         <v>3</v>
       </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
       <c r="D7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -9942,10 +9953,10 @@
         <v>16</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -9994,13 +10005,13 @@
         <v>139</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -10352,7 +10363,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BBD4D6-0DB8-4FD6-B329-B5CC2159D401}">
   <sheetPr codeName="Sheet9"/>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.109375" customWidth="1"/>
@@ -11042,22 +11053,20 @@
         <v>137</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>11</v>
+        <v>509</v>
       </c>
       <c r="B21" t="s">
         <v>157</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>177</v>
+        <v>510</v>
       </c>
       <c r="G21" s="1">
-        <v>2022</v>
-      </c>
-      <c r="H21" s="19">
-        <v>44743</v>
-      </c>
+        <v>2021</v>
+      </c>
+      <c r="H21" s="19"/>
       <c r="I21" s="1" t="s">
         <v>157</v>
       </c>
@@ -11068,110 +11077,133 @@
         <v>175</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>294</v>
-      </c>
-      <c r="E22" t="s">
+    <row r="22" spans="1:13" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" t="s">
         <v>157</v>
       </c>
+      <c r="F22" s="1" t="s">
+        <v>177</v>
+      </c>
       <c r="G22" s="1">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="H22" s="19">
-        <v>43101</v>
+        <v>44743</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>175</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>9</v>
+    <row r="23" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>294</v>
       </c>
       <c r="E23" t="s">
         <v>157</v>
       </c>
-      <c r="F23"/>
       <c r="G23" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H23">
-        <v>2007</v>
+        <v>2015</v>
+      </c>
+      <c r="H23" s="19">
+        <v>43101</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>19</v>
+    <row r="24" spans="1:13" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E24" t="s">
         <v>157</v>
       </c>
+      <c r="F24"/>
       <c r="G24" s="1">
-        <v>2018</v>
-      </c>
-      <c r="H24" s="19">
-        <v>43101</v>
+        <v>2025</v>
+      </c>
+      <c r="H24">
+        <v>2007</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="L24" t="s">
-        <v>395</v>
+      <c r="L24" s="1" t="s">
+        <v>397</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-      <c r="H25" s="19"/>
-      <c r="K25" s="1"/>
-      <c r="M25" s="1"/>
-    </row>
-    <row r="27" spans="1:13" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="21"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="A25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" t="s">
+        <v>157</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H25" s="19">
+        <v>43101</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="L25" t="s">
+        <v>395</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="H26" s="19"/>
+      <c r="K26" s="1"/>
+      <c r="M26" s="1"/>
     </row>
     <row r="28" spans="1:13" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="21"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
+      <c r="K28" s="1"/>
     </row>
     <row r="29" spans="1:13" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -11179,43 +11211,52 @@
       <c r="I29" s="1"/>
     </row>
     <row r="30" spans="1:13" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="2"/>
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
-      <c r="E30" s="21"/>
+      <c r="E30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="K30" s="1"/>
     </row>
     <row r="31" spans="1:13" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="1"/>
+      <c r="B31" s="2"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="G31"/>
+      <c r="E31" s="21"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
+      <c r="K31" s="1"/>
     </row>
     <row r="32" spans="1:13" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
+      <c r="B32" s="1"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
       <c r="G32"/>
       <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
     </row>
     <row r="33" spans="1:9" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="G33"/>
       <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L26">
-    <sortCondition ref="K3:K26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:L27">
+    <sortCondition ref="K3:K27"/>
   </sortState>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
   <pageSetup paperSize="0" fitToWidth="0" fitToHeight="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
@@ -11244,7 +11285,7 @@
       <c r="H1" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="I1" s="41"/>
+      <c r="I1" s="38"/>
       <c r="J1" s="27" t="s">
         <v>497</v>
       </c>
@@ -11261,26 +11302,26 @@
       <c r="Q1" s="29"/>
     </row>
     <row r="2" spans="5:17" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="34" t="s">
         <v>486</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="G2" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="38"/>
-      <c r="J2" s="37" t="s">
+      <c r="I2" s="35"/>
+      <c r="J2" s="34" t="s">
         <v>499</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="K2" s="36" t="s">
         <v>498</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="36" t="s">
         <v>464</v>
       </c>
       <c r="M2" s="30"/>
@@ -11290,26 +11331,26 @@
       <c r="Q2" s="29"/>
     </row>
     <row r="3" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="34" t="s">
         <v>487</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="G3" s="37" t="s">
+      <c r="G3" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="38"/>
-      <c r="J3" s="39" t="s">
+      <c r="I3" s="35"/>
+      <c r="J3" s="36" t="s">
         <v>500</v>
       </c>
-      <c r="K3" s="39" t="s">
+      <c r="K3" s="36" t="s">
         <v>501</v>
       </c>
-      <c r="L3" s="39" t="s">
+      <c r="L3" s="36" t="s">
         <v>278</v>
       </c>
       <c r="M3" s="30"/>
@@ -11319,26 +11360,26 @@
       <c r="Q3" s="29"/>
     </row>
     <row r="4" spans="5:17" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="34" t="s">
         <v>204</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="37" t="s">
+      <c r="G4" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="38"/>
-      <c r="J4" s="39" t="s">
+      <c r="I4" s="35"/>
+      <c r="J4" s="36" t="s">
         <v>502</v>
       </c>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="36" t="s">
         <v>503</v>
       </c>
-      <c r="L4" s="39" t="s">
+      <c r="L4" s="36" t="s">
         <v>289</v>
       </c>
       <c r="M4" s="30"/>
@@ -11348,24 +11389,24 @@
       <c r="Q4" s="29"/>
     </row>
     <row r="5" spans="5:17" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="38"/>
-      <c r="J5" s="39" t="s">
+      <c r="I5" s="35"/>
+      <c r="J5" s="36" t="s">
         <v>504</v>
       </c>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39" t="s">
+      <c r="K5" s="36"/>
+      <c r="L5" s="36" t="s">
         <v>249</v>
       </c>
       <c r="M5" s="30"/>
@@ -11375,26 +11416,26 @@
       <c r="Q5" s="29"/>
     </row>
     <row r="6" spans="5:17" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="G6" s="37" t="s">
+      <c r="G6" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="38"/>
-      <c r="J6" s="39" t="s">
+      <c r="I6" s="35"/>
+      <c r="J6" s="36" t="s">
         <v>506</v>
       </c>
-      <c r="K6" s="39" t="s">
+      <c r="K6" s="36" t="s">
         <v>505</v>
       </c>
-      <c r="L6" s="39" t="s">
+      <c r="L6" s="36" t="s">
         <v>289</v>
       </c>
       <c r="M6" s="30"/>
@@ -11404,26 +11445,26 @@
       <c r="Q6" s="29"/>
     </row>
     <row r="7" spans="5:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="34" t="s">
         <v>209</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="G7" s="34" t="s">
         <v>461</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="38"/>
-      <c r="J7" s="39" t="s">
+      <c r="I7" s="35"/>
+      <c r="J7" s="36" t="s">
         <v>507</v>
       </c>
-      <c r="K7" s="39" t="s">
+      <c r="K7" s="36" t="s">
         <v>506</v>
       </c>
-      <c r="L7" s="39" t="s">
+      <c r="L7" s="36" t="s">
         <v>290</v>
       </c>
       <c r="M7" s="30"/>
@@ -11433,26 +11474,26 @@
       <c r="Q7" s="29"/>
     </row>
     <row r="8" spans="5:17" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="34" t="s">
         <v>488</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="G8" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="38"/>
-      <c r="J8" s="39" t="s">
+      <c r="I8" s="35"/>
+      <c r="J8" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="L8" s="39" t="s">
+      <c r="L8" s="36" t="s">
         <v>291</v>
       </c>
       <c r="M8" s="30"/>
@@ -11462,26 +11503,26 @@
       <c r="Q8" s="29"/>
     </row>
     <row r="9" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="38"/>
-      <c r="J9" s="39" t="s">
+      <c r="I9" s="35"/>
+      <c r="J9" s="36" t="s">
         <v>281</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="K9" s="36" t="s">
         <v>284</v>
       </c>
-      <c r="L9" s="39" t="s">
+      <c r="L9" s="36" t="s">
         <v>292</v>
       </c>
       <c r="M9" s="30"/>
@@ -11491,22 +11532,22 @@
       <c r="Q9" s="29"/>
     </row>
     <row r="10" spans="5:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E10" s="40" t="s">
+      <c r="E10" s="37" t="s">
         <v>489</v>
       </c>
-      <c r="F10" s="40" t="s">
+      <c r="F10" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="37" t="s">
         <v>264</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="38"/>
-      <c r="J10" s="38"/>
-      <c r="K10" s="38"/>
-      <c r="L10" s="39" t="s">
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="36" t="s">
         <v>508</v>
       </c>
       <c r="M10" s="30"/>
@@ -11516,26 +11557,26 @@
       <c r="Q10" s="29"/>
     </row>
     <row r="11" spans="5:17" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="34" t="s">
         <v>197</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="34" t="s">
         <v>218</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="34" t="s">
         <v>277</v>
       </c>
-      <c r="H11" s="37" t="s">
+      <c r="H11" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="38"/>
-      <c r="J11" s="39" t="s">
+      <c r="I11" s="35"/>
+      <c r="J11" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="K11" s="39" t="s">
+      <c r="K11" s="36" t="s">
         <v>283</v>
       </c>
-      <c r="L11" s="39" t="s">
+      <c r="L11" s="36" t="s">
         <v>292</v>
       </c>
       <c r="M11" s="30"/>
@@ -11545,26 +11586,26 @@
       <c r="Q11" s="29"/>
     </row>
     <row r="12" spans="5:17" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="34" t="s">
         <v>490</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="H12" s="37" t="s">
+      <c r="H12" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I12" s="38"/>
-      <c r="J12" s="37" t="s">
+      <c r="I12" s="35"/>
+      <c r="J12" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="K12" s="39" t="s">
+      <c r="K12" s="36" t="s">
         <v>496</v>
       </c>
-      <c r="L12" s="39"/>
+      <c r="L12" s="36"/>
       <c r="M12" s="30"/>
       <c r="N12" s="29"/>
       <c r="O12" s="29"/>
@@ -11572,26 +11613,26 @@
       <c r="Q12" s="29"/>
     </row>
     <row r="13" spans="5:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="34" t="s">
         <v>200</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="G13" s="37" t="s">
+      <c r="G13" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="38"/>
-      <c r="J13" s="39" t="s">
+      <c r="I13" s="35"/>
+      <c r="J13" s="36" t="s">
         <v>493</v>
       </c>
-      <c r="K13" s="39" t="s">
+      <c r="K13" s="36" t="s">
         <v>494</v>
       </c>
-      <c r="L13" s="39" t="s">
+      <c r="L13" s="36" t="s">
         <v>493</v>
       </c>
       <c r="M13" s="30"/>
@@ -11601,26 +11642,26 @@
       <c r="Q13" s="29"/>
     </row>
     <row r="14" spans="5:17" ht="216" x14ac:dyDescent="0.3">
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="G14" s="37" t="s">
+      <c r="G14" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="H14" s="37" t="s">
+      <c r="H14" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39" t="s">
+      <c r="I14" s="35"/>
+      <c r="J14" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="K14" s="39" t="s">
+      <c r="K14" s="36" t="s">
         <v>337</v>
       </c>
-      <c r="L14" s="39" t="s">
+      <c r="L14" s="36" t="s">
         <v>280</v>
       </c>
       <c r="M14" s="30"/>
@@ -11630,24 +11671,24 @@
       <c r="Q14" s="29"/>
     </row>
     <row r="15" spans="5:17" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="34" t="s">
         <v>492</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="34" t="s">
         <v>212</v>
       </c>
-      <c r="G15" s="37" t="s">
+      <c r="G15" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="H15" s="37" t="s">
+      <c r="H15" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I15" s="38"/>
-      <c r="J15" s="37" t="s">
+      <c r="I15" s="35"/>
+      <c r="J15" s="34" t="s">
         <v>286</v>
       </c>
-      <c r="K15" s="39"/>
-      <c r="L15" s="39" t="s">
+      <c r="K15" s="36"/>
+      <c r="L15" s="36" t="s">
         <v>293</v>
       </c>
       <c r="M15" s="30"/>
@@ -11657,26 +11698,26 @@
       <c r="Q15" s="29"/>
     </row>
     <row r="16" spans="5:17" ht="72" x14ac:dyDescent="0.3">
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="F16" s="40" t="s">
+      <c r="F16" s="37" t="s">
         <v>220</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="H16" s="37" t="s">
+      <c r="H16" s="34" t="s">
         <v>273</v>
       </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="39" t="s">
+      <c r="I16" s="35"/>
+      <c r="J16" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="K16" s="39" t="s">
+      <c r="K16" s="36" t="s">
         <v>288</v>
       </c>
-      <c r="L16" s="39"/>
+      <c r="L16" s="36"/>
       <c r="M16" s="30"/>
       <c r="N16" s="29"/>
       <c r="O16" s="29"/>
@@ -11684,26 +11725,26 @@
       <c r="Q16" s="29"/>
     </row>
     <row r="17" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="34" t="s">
         <v>207</v>
       </c>
-      <c r="F17" s="37" t="s">
+      <c r="F17" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="G17" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="H17" s="37" t="s">
+      <c r="H17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="38"/>
-      <c r="J17" s="39" t="s">
+      <c r="I17" s="35"/>
+      <c r="J17" s="36" t="s">
         <v>495</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="36" t="s">
         <v>495</v>
       </c>
-      <c r="L17" s="39" t="s">
+      <c r="L17" s="36" t="s">
         <v>495</v>
       </c>
       <c r="M17" s="30"/>

--- a/DarkJargon_SoK_taxonomy_tables.xlsx
+++ b/DarkJargon_SoK_taxonomy_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniluxembourg-my.sharepoint.com/personal/laura_bernardy_uni_lu/Documents/Documents/GitHub/DarkJargon-SOK-USENIX26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{889C5A6C-99FE-49D5-B057-CE0D9F29AF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{09900854-4285-4AAF-83CB-19AA28E01EAF}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{889C5A6C-99FE-49D5-B057-CE0D9F29AF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64F50139-D286-411C-BE75-805E0432F017}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" firstSheet="1" activeTab="4" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="512">
   <si>
     <t>Approaches</t>
   </si>
@@ -2541,6 +2541,9 @@
   </si>
   <si>
     <t>Seventh Workshop on Noisy User-generated Text (W-NUT 2021)</t>
+  </si>
+  <si>
+    <t>korean (but approach is claimed language agnostic)</t>
   </si>
 </sst>
 </file>
@@ -6753,6 +6756,10 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -8554,7 +8561,7 @@
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="J8" s="11" t="s">
         <v>424</v>
@@ -8678,13 +8685,15 @@
       <c r="S10" s="26"/>
       <c r="T10" s="26"/>
       <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
+      <c r="V10" s="26" t="s">
+        <v>46</v>
+      </c>
       <c r="W10" s="26"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="J11" s="11" t="s">
         <v>416</v>
@@ -8969,7 +8978,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="216" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="J17" s="11" t="s">
         <v>417</v>
@@ -9008,7 +9017,7 @@
         <v>90</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>91</v>
+        <v>511</v>
       </c>
       <c r="W17" s="11" t="s">
         <v>438</v>

--- a/DarkJargon_SoK_taxonomy_tables.xlsx
+++ b/DarkJargon_SoK_taxonomy_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniluxembourg-my.sharepoint.com/personal/laura_bernardy_uni_lu/Documents/Documents/GitHub/DarkJargon-SOK-USENIX26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{889C5A6C-99FE-49D5-B057-CE0D9F29AF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64F50139-D286-411C-BE75-805E0432F017}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{889C5A6C-99FE-49D5-B057-CE0D9F29AF69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{562976C3-569B-428F-AF1E-703AD684CFEF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="9" xr2:uid="{04FFE807-261D-4A06-984B-A3A8A34061AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="510">
   <si>
     <t>Approaches</t>
   </si>
@@ -500,9 +500,6 @@
     <t>Springer</t>
   </si>
   <si>
-    <t>Scholar</t>
-  </si>
-  <si>
     <t>other</t>
   </si>
   <si>
@@ -1083,9 +1080,6 @@
   </si>
   <si>
     <t>annotation/creation</t>
-  </si>
-  <si>
-    <t>Mentioned Resources</t>
   </si>
   <si>
     <t>manual annotation: category per document</t>
@@ -2821,7 +2815,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{1EB5855D-A8E9-42DE-A743-8C096ABB6D75}"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2839,7 +2833,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3609,7 +3603,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -3697,9 +3691,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>database_dist!$A$11:$A$18</c:f>
+              <c:f>database_dist!$A$11:$A$17</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Springer</c:v>
                 </c:pt>
@@ -3716,12 +3710,9 @@
                   <c:v>IEEE Xplore</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Scholar</c:v>
+                  <c:v>sciencedirect</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>sciencedirect</c:v>
-                </c:pt>
-                <c:pt idx="7">
                   <c:v>other</c:v>
                 </c:pt>
               </c:strCache>
@@ -3729,15 +3720,15 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>database_dist!$B$11:$B$18</c:f>
+              <c:f>database_dist!$B$11:$B$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -3749,10 +3740,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3840,9 +3831,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>database_dist!$A$11:$A$18</c:f>
+              <c:f>database_dist!$A$11:$A$17</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Springer</c:v>
                 </c:pt>
@@ -3859,12 +3850,9 @@
                   <c:v>IEEE Xplore</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Scholar</c:v>
+                  <c:v>sciencedirect</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>sciencedirect</c:v>
-                </c:pt>
-                <c:pt idx="7">
                   <c:v>other</c:v>
                 </c:pt>
               </c:strCache>
@@ -3872,17 +3860,17 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>database_dist!$C$11:$C$18</c:f>
+              <c:f>database_dist!$C$11:$C$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -4018,9 +4006,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>database_dist!$A$11:$A$18</c:f>
+              <c:f>database_dist!$A$11:$A$17</c:f>
               <c:strCache>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Springer</c:v>
                 </c:pt>
@@ -4037,12 +4025,9 @@
                   <c:v>IEEE Xplore</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Scholar</c:v>
+                  <c:v>sciencedirect</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>sciencedirect</c:v>
-                </c:pt>
-                <c:pt idx="7">
                   <c:v>other</c:v>
                 </c:pt>
               </c:strCache>
@@ -4050,10 +4035,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>database_dist!$D$11:$D$18</c:f>
+              <c:f>database_dist!$D$11:$D$17</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -4070,13 +4055,10 @@
                   <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3</c:v>
+                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4376,7 +4358,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
@@ -5850,918 +5832,12 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>319928</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>42582</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D533F50-A61B-42EB-AE6B-BC3D56DD6A67}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="2148728" cy="10177182"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Objectiv</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>e Type </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>(O)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>O1 Term-level detection</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>: identify jargon tokens/phrases</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>O2 Post-level detection</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>: classify posts containing jargon</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>O3 Interpretation / grounding</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>: map jargon → meaning/entity</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>O4 Analysis / reasoning</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>: probing, evaluation, or sociolinguistic analysis</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Jargon Type (T)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>T1 Slang</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>T2 Euphemisms</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> (indirect references)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>R3 Obfuscations / variants</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>T4 Contextual semantic shift</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Model (M)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M1 Lexicon / rules</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M2 Probabilistic</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> (LDA und co)</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M3 Embeddings</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M4  Classifier</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M5 Contextual</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M5 Graph / syntactic models</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M6 Unsupervised / clustering</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M7 Causal/Autoregressive</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>LLMs</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>M8 Mathmatical/Statistical Measures</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Supervision (S)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>S1 Unsupervised</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>S2 Weak / distant</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>S3Supervised</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>S4 Semi/self-supervised</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Evaluation (E)</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>E1 Token/span metrics</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>E2 Post/Sentence-level metrics</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>E3 Ranking / discovery metrics</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>E4 Human / qualitative analysis</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050" b="1" i="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>E5 Diagnostic / probing</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1050">
-              <a:effectLst/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -7079,7 +6155,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD7FE90-D187-4CE7-95A5-0983D5C5472A}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:W18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="44.44140625" customWidth="1"/>
@@ -7318,7 +6394,7 @@
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
     </row>
-    <row r="9" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:23" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -7546,7 +6622,7 @@
     </row>
     <row r="17" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -7573,7 +6649,7 @@
     </row>
     <row r="18" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -7606,8 +6682,8 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF88FA73-5CF9-4E00-9308-E51E6D45B492}">
   <sheetPr codeName="Sheet12"/>
-  <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="16.33203125" customWidth="1"/>
     <col min="10" max="10" width="37.44140625" customWidth="1"/>
@@ -7615,598 +6691,581 @@
   <sheetData>
     <row r="1" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="H1" t="s">
         <v>338</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>299</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="H1" t="s">
-        <v>339</v>
-      </c>
       <c r="I1" s="1" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2022</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
     </row>
     <row r="3" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C3" s="1">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E3" s="21" t="s">
         <v>308</v>
       </c>
+      <c r="E3" s="1" t="s">
+        <v>306</v>
+      </c>
       <c r="F3" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>341</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2019</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="G4" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="C5" s="1">
         <v>2017</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H4" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="F5" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="C5" s="1">
-        <v>2019</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>313</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="K5" t="s">
-        <v>342</v>
+        <v>302</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>303</v>
+      <c r="A6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>302</v>
       </c>
       <c r="C6" s="1">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>345</v>
+        <v>297</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>316</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="H6" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="K6" t="s">
         <v>346</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="K6" s="1" t="s">
+    </row>
+    <row r="7" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2007</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="E7" t="s">
+        <v>323</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="K7" t="s">
         <v>347</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>294</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2015</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="K7" t="s">
+    <row r="8" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="1">
+        <v>2018</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2007</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="E8" t="s">
-        <v>324</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>335</v>
+      <c r="I8" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="K8" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H9" s="1" t="s">
+    <row r="9" spans="1:12" s="40" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="I9" s="1" t="s">
+    </row>
+    <row r="10" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>271</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1">
+        <v>2021</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="K9" t="s">
+      <c r="E10" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" s="40" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="40" t="s">
+      <c r="I10" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>272</v>
+        <v>461</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>353</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>334</v>
+        <v>354</v>
+      </c>
+      <c r="G11" t="s">
+        <v>156</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>463</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1">
-        <v>2018</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="E12" s="21" t="s">
+      <c r="K11" t="s">
         <v>355</v>
       </c>
-      <c r="F12" s="1" t="s">
+    </row>
+    <row r="12" spans="1:12" s="39" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="G12" t="s">
-        <v>157</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="K12" t="s">
+    </row>
+    <row r="13" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2023</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" s="39" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="39" t="s">
+      <c r="F13" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>342</v>
-      </c>
       <c r="C14" s="1">
-        <v>2023</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>303</v>
+        <v>2016</v>
+      </c>
+      <c r="D14" t="s">
+        <v>302</v>
       </c>
       <c r="E14" t="s">
         <v>359</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>306</v>
+      <c r="F14" t="s">
+        <v>360</v>
+      </c>
+      <c r="G14" t="s">
+        <v>156</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>360</v>
+        <v>319</v>
+      </c>
+      <c r="J14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>363</v>
       </c>
       <c r="C15" s="1">
-        <v>2016</v>
-      </c>
-      <c r="D15" t="s">
-        <v>303</v>
-      </c>
-      <c r="E15" t="s">
+        <v>2022</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>364</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="F15" t="s">
-        <v>362</v>
-      </c>
-      <c r="G15" t="s">
-        <v>157</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="J15" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="K15" s="1" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>369</v>
       </c>
       <c r="C16" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>366</v>
+        <v>302</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="53.4" x14ac:dyDescent="0.3">
+        <v>361</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+    </row>
+    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>371</v>
-      </c>
+        <v>347</v>
+      </c>
+      <c r="B17" s="23"/>
       <c r="C17" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>372</v>
+        <v>2018</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="E17" t="s">
+        <v>373</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="s">
-        <v>363</v>
+        <v>310</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="B18" s="23"/>
+        <v>376</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>377</v>
+      </c>
       <c r="C18" s="1">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E18" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="I18" s="1"/>
+        <v>380</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>381</v>
+      </c>
       <c r="J18" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C19" s="1">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E19" t="s">
-        <v>380</v>
+        <v>383</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>383</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>311</v>
+        <v>361</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C20" s="1">
-        <v>2017</v>
+        <v>2024</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>385</v>
+        <v>302</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
+        <v>156</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>389</v>
+      </c>
       <c r="J20" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-    </row>
-    <row r="21" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C21" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="F21" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>392</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A10:XFD10"/>
-    <mergeCell ref="A13:XFD13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A9:XFD9"/>
+    <mergeCell ref="A12:XFD12"/>
   </mergeCells>
   <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
 </worksheet>
@@ -8216,7 +7275,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00128613-88F2-454B-981C-0D08A4EB964B}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:Z40"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="8.88671875" customWidth="1"/>
     <col min="10" max="10" width="29.77734375" customWidth="1"/>
@@ -8236,25 +7295,25 @@
     <row r="1" spans="1:26" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="6"/>
       <c r="J1" s="7" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="L1" s="7" t="s">
         <v>31</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N1" s="7" t="s">
         <v>32</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="P1" s="7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="Q1" s="7" t="s">
         <v>33</v>
@@ -8281,31 +7340,31 @@
     <row r="2" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="J2" s="11" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N2" s="11" t="s">
         <v>48</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q2" s="11" t="s">
         <v>100</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="S2" s="11" t="s">
         <v>101</v>
@@ -8320,29 +7379,29 @@
         <v>46</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="J3" s="11" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="K3" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="M3" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="L3" s="11" t="s">
-        <v>442</v>
-      </c>
-      <c r="M3" s="11" t="s">
-        <v>214</v>
-      </c>
       <c r="N3" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O3" s="11"/>
       <c r="P3" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q3" s="11" t="s">
         <v>66</v>
@@ -8363,7 +7422,7 @@
         <v>46</v>
       </c>
       <c r="W3" s="11" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -8372,25 +7431,25 @@
     <row r="4" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="J4" s="11" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="N4" s="11" t="s">
         <v>116</v>
       </c>
       <c r="O4" s="11" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q4" s="11" t="s">
         <v>49</v>
@@ -8411,7 +7470,7 @@
         <v>46</v>
       </c>
       <c r="W4" s="25" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -8420,25 +7479,25 @@
     <row r="5" spans="1:26" ht="216" x14ac:dyDescent="0.3">
       <c r="A5" s="9"/>
       <c r="J5" s="11" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="N5" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q5" s="11" t="s">
         <v>93</v>
@@ -8459,7 +7518,7 @@
         <v>46</v>
       </c>
       <c r="W5" s="25" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -8468,25 +7527,25 @@
     <row r="6" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
       <c r="J6" s="11" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="O6" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P6" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q6" s="11" t="s">
         <v>117</v>
@@ -8507,7 +7566,7 @@
         <v>46</v>
       </c>
       <c r="W6" s="11" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -8516,25 +7575,25 @@
     <row r="7" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="J7" s="11" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="K7" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="N7" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="L7" s="11" t="s">
-        <v>443</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="N7" s="11" t="s">
-        <v>209</v>
-      </c>
       <c r="O7" s="11" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="P7" s="11" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="Q7" s="11" t="s">
         <v>41</v>
@@ -8555,34 +7614,34 @@
         <v>46</v>
       </c>
       <c r="W7" s="24" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
       <c r="Z7" s="1"/>
     </row>
-    <row r="8" spans="1:26" ht="144" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="6"/>
       <c r="J8" s="11" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="N8" s="11" t="s">
         <v>85</v>
       </c>
       <c r="O8" s="11" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>111</v>
@@ -8603,7 +7662,7 @@
         <v>77</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -8612,25 +7671,25 @@
     <row r="9" spans="1:26" ht="144" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="J9" s="11" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="L9" s="11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="N9" s="11" t="s">
         <v>99</v>
       </c>
       <c r="O9" s="11" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q9" s="11" t="s">
         <v>72</v>
@@ -8651,7 +7710,7 @@
         <v>77</v>
       </c>
       <c r="W9" s="11" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="1"/>
@@ -8660,25 +7719,25 @@
     <row r="10" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A10" s="9"/>
       <c r="J10" s="11" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="K10" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="N10" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O10" s="26" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="P10" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q10" s="26"/>
       <c r="R10" s="26"/>
@@ -8693,28 +7752,28 @@
       <c r="Y10" s="1"/>
       <c r="Z10" s="1"/>
     </row>
-    <row r="11" spans="1:26" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="9"/>
       <c r="J11" s="11" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="K11" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="M11" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="L11" s="11" t="s">
-        <v>445</v>
-      </c>
-      <c r="M11" s="11" t="s">
+      <c r="N11" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="N11" s="11" t="s">
-        <v>218</v>
-      </c>
       <c r="O11" s="11" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="P11" s="11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q11" s="11" t="s">
         <v>79</v>
@@ -8743,25 +7802,25 @@
     </row>
     <row r="12" spans="1:26" ht="331.2" x14ac:dyDescent="0.3">
       <c r="J12" s="11" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="K12" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="M12" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="N12" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="N12" s="11" t="s">
-        <v>224</v>
-      </c>
       <c r="O12" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P12" s="11" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Q12" s="11" t="s">
         <v>105</v>
@@ -8782,7 +7841,7 @@
         <v>46</v>
       </c>
       <c r="W12" s="11" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="1"/>
@@ -8792,25 +7851,25 @@
       <c r="A13" s="6"/>
       <c r="I13" s="10"/>
       <c r="J13" s="11" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="K13" s="11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="M13" s="11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O13" s="11" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="P13" s="11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="Q13" s="11" t="s">
         <v>127</v>
@@ -8837,25 +7896,25 @@
     <row r="14" spans="1:26" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A14" s="9"/>
       <c r="J14" s="11" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="K14" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M14" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="O14" s="11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P14" s="11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q14" s="11" t="s">
         <v>54</v>
@@ -8876,7 +7935,7 @@
         <v>46</v>
       </c>
       <c r="W14" s="11" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="X14" s="1"/>
       <c r="Y14" s="1"/>
@@ -8885,25 +7944,25 @@
     <row r="15" spans="1:26" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A15" s="9"/>
       <c r="J15" s="11" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="K15" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M15" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="N15" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="N15" s="11" t="s">
-        <v>212</v>
-      </c>
       <c r="O15" s="11" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="P15" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q15" s="11" t="s">
         <v>60</v>
@@ -8924,7 +7983,7 @@
         <v>46</v>
       </c>
       <c r="W15" s="11" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="X15" s="1"/>
       <c r="Y15" s="1"/>
@@ -8933,31 +7992,31 @@
     <row r="16" spans="1:26" ht="288" x14ac:dyDescent="0.3">
       <c r="A16" s="9"/>
       <c r="J16" s="11" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="K16" s="26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="M16" s="11" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="N16" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O16" s="26" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="P16" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Q16" s="26" t="s">
         <v>122</v>
       </c>
       <c r="R16" s="11" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="S16" s="26" t="s">
         <v>123</v>
@@ -8972,34 +8031,34 @@
         <v>77</v>
       </c>
       <c r="W16" s="11" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="X16" s="1"/>
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="216" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A17" s="9"/>
       <c r="J17" s="11" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="K17" s="11" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="M17" s="11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O17" s="11" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="P17" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q17" s="11" t="s">
         <v>86</v>
@@ -9017,10 +8076,10 @@
         <v>90</v>
       </c>
       <c r="V17" s="11" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="W17" s="11" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="X17" s="1"/>
       <c r="Y17" s="1"/>
@@ -9400,7 +8459,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3848A618-F519-44D4-8E08-F26788D24310}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="3" width="11.5546875" customWidth="1"/>
@@ -9413,40 +8472,40 @@
         <v>136</v>
       </c>
       <c r="B1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="C1" t="s">
-        <v>234</v>
-      </c>
-      <c r="D1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>233</v>
       </c>
       <c r="F1" t="s">
         <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="82.8" x14ac:dyDescent="0.3">
@@ -9454,10 +8513,10 @@
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E3" s="32" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F3" s="2"/>
     </row>
@@ -9466,10 +8525,10 @@
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F4" s="2"/>
     </row>
@@ -9478,119 +8537,119 @@
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" t="s">
         <v>240</v>
-      </c>
-      <c r="C6" t="s">
-        <v>241</v>
       </c>
       <c r="E6" s="1">
         <v>0.6</v>
       </c>
       <c r="F6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B8" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C8" t="s">
+        <v>242</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>244</v>
-      </c>
       <c r="F8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C9" t="s">
         <v>240</v>
       </c>
-      <c r="C9" t="s">
-        <v>241</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
       <c r="D10" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B11" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E11" s="1">
         <v>0.31</v>
       </c>
       <c r="F11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" t="s">
         <v>240</v>
-      </c>
-      <c r="C12" t="s">
-        <v>241</v>
       </c>
       <c r="E12" s="1">
         <v>0.60560000000000003</v>
@@ -9598,189 +8657,189 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B13" t="s">
+        <v>239</v>
+      </c>
+      <c r="C13" t="s">
         <v>240</v>
-      </c>
-      <c r="C13" t="s">
-        <v>241</v>
       </c>
       <c r="E13" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="C14" s="20"/>
       <c r="D14" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C16" t="s">
         <v>240</v>
-      </c>
-      <c r="C16" t="s">
-        <v>241</v>
       </c>
       <c r="E16" s="1">
         <v>0.57999999999999996</v>
       </c>
       <c r="F16" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2"/>
       <c r="C17" s="20"/>
       <c r="D17" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B18" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C18" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>251</v>
-      </c>
       <c r="F18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C20" t="s">
+        <v>252</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="F20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="D21" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C22" t="s">
         <v>256</v>
       </c>
-      <c r="C22" t="s">
+      <c r="E22" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="F22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E23" s="1">
         <v>94.3</v>
       </c>
       <c r="F23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -9793,7 +8852,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{399DB999-9283-4751-BBD0-238C098D8C5B}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -9978,7 +9037,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C01F8EC5-B561-4123-A5F6-54D916B5F663}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A10:D18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="35.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
@@ -10014,10 +9073,10 @@
         <v>139</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -10058,38 +9117,36 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18">
-        <v>3</v>
-      </c>
       <c r="D18">
-        <v>3</v>
+        <f>SUM(D11:D17)</f>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -10102,7 +9159,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AA0438A-EE17-4255-B1AE-346A842E6C2A}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -10114,7 +9171,7 @@
         <v>134</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -10127,7 +9184,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B3" s="16">
         <v>1</v>
@@ -10143,7 +9200,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B5" s="16">
         <v>1</v>
@@ -10183,7 +9240,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E2653FE-28AA-46DB-9FB7-F833B0E0256D}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.21875" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" customWidth="1"/>
@@ -10191,29 +9248,29 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>455</v>
+      </c>
+      <c r="B1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C1" t="s">
         <v>457</v>
-      </c>
-      <c r="B1" t="s">
-        <v>458</v>
-      </c>
-      <c r="C1" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>75</v>
@@ -10221,18 +9278,18 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>75</v>
@@ -10240,7 +9297,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>75</v>
@@ -10248,29 +9305,29 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>44</v>
@@ -10278,10 +9335,10 @@
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C10" t="s">
         <v>75</v>
@@ -10289,7 +9346,7 @@
     </row>
     <row r="11" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>75</v>
@@ -10300,40 +9357,40 @@
     </row>
     <row r="12" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>44</v>
@@ -10344,21 +9401,21 @@
     </row>
     <row r="16" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s">
         <v>57</v>
@@ -10373,7 +9430,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BBD4D6-0DB8-4FD6-B329-B5CC2159D401}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="A1:M34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="42.109375" customWidth="1"/>
     <col min="2" max="4" width="19" customWidth="1"/>
@@ -10387,43 +9444,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>152</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>132</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>153</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>133</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -10431,12 +9488,12 @@
         <v>59</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="F2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G2" s="1">
         <v>2025</v>
@@ -10445,16 +9502,16 @@
         <v>45870</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>138</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>136</v>
@@ -10465,12 +9522,12 @@
         <v>65</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G3" s="1">
         <v>2023</v>
@@ -10479,16 +9536,16 @@
         <v>45108</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>139</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>136</v>
@@ -10499,12 +9556,12 @@
         <v>71</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G4" s="1">
         <v>2022</v>
@@ -10513,16 +9570,16 @@
         <v>44593</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>140</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>136</v>
@@ -10533,12 +9590,12 @@
         <v>98</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="F5" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G5" s="18">
         <v>2025</v>
@@ -10547,16 +9604,16 @@
         <v>45839</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>140</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>136</v>
@@ -10567,12 +9624,12 @@
         <v>40</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G6" s="1">
         <v>2024</v>
@@ -10581,16 +9638,16 @@
         <v>45413</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>140</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>136</v>
@@ -10601,12 +9658,12 @@
         <v>92</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="F7" s="18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G7" s="18">
         <v>2021</v>
@@ -10615,16 +9672,16 @@
         <v>44197</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>140</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>136</v>
@@ -10637,10 +9694,10 @@
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G8" s="1">
         <v>2024</v>
@@ -10653,10 +9710,10 @@
         <v>141</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>136</v>
@@ -10667,12 +9724,12 @@
         <v>110</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G9" s="1">
         <v>2016</v>
@@ -10681,16 +9738,16 @@
         <v>42614</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>136</v>
@@ -10701,12 +9758,12 @@
         <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G10" s="1">
         <v>2021</v>
@@ -10715,16 +9772,16 @@
         <v>44317</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>136</v>
@@ -10735,12 +9792,12 @@
         <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G11" s="1">
         <v>2023</v>
@@ -10749,16 +9806,16 @@
         <v>45139</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>136</v>
@@ -10769,12 +9826,12 @@
         <v>121</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G12" s="1">
         <v>2017</v>
@@ -10783,16 +9840,16 @@
         <v>42856</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J12" s="1" t="s">
         <v>142</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>136</v>
@@ -10804,11 +9861,11 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D13" s="1"/>
       <c r="F13" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G13" s="1">
         <v>2024</v>
@@ -10817,16 +9874,16 @@
         <v>45383</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M13" s="1" t="s">
         <v>136</v>
@@ -10837,12 +9894,12 @@
         <v>53</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="F14" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G14" s="1">
         <v>2023</v>
@@ -10851,16 +9908,16 @@
         <v>45108</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>136</v>
@@ -10871,12 +9928,12 @@
         <v>104</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="F15" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G15" s="1">
         <v>2018</v>
@@ -10885,16 +9942,16 @@
         <v>43313</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>136</v>
@@ -10906,11 +9963,11 @@
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D16" s="1"/>
       <c r="F16" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G16" s="1">
         <v>2024</v>
@@ -10919,16 +9976,16 @@
         <v>45413</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>143</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>136</v>
@@ -10936,13 +9993,13 @@
     </row>
     <row r="17" spans="1:13" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="B17" t="s">
-        <v>157</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="G17" s="1">
         <v>2021</v>
@@ -10951,16 +10008,16 @@
         <v>44378</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J17" s="1" t="s">
         <v>140</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>136</v>
@@ -10971,10 +10028,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G18" s="1">
         <v>2017</v>
@@ -10983,16 +10040,16 @@
         <v>42826</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>139</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>137</v>
@@ -11003,10 +10060,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G19" s="1">
         <v>2019</v>
@@ -11015,16 +10072,16 @@
         <v>43617</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>143</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>136</v>
@@ -11035,10 +10092,10 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G20" s="1">
         <v>2017</v>
@@ -11047,16 +10104,16 @@
         <v>42979</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>139</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>137</v>
@@ -11064,29 +10121,29 @@
     </row>
     <row r="21" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="G21" s="1">
         <v>2021</v>
       </c>
       <c r="H21" s="19"/>
       <c r="I21" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>139</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>137</v>
@@ -11097,10 +10154,10 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G22" s="1">
         <v>2022</v>
@@ -11109,16 +10166,16 @@
         <v>44743</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J22" s="1" t="s">
         <v>139</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>137</v>
@@ -11126,10 +10183,10 @@
     </row>
     <row r="23" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G23" s="1">
         <v>2015</v>
@@ -11138,10 +10195,10 @@
         <v>43101</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>137</v>
@@ -11152,7 +10209,7 @@
         <v>9</v>
       </c>
       <c r="E24" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F24"/>
       <c r="G24" s="1">
@@ -11162,10 +10219,10 @@
         <v>2007</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>137</v>
@@ -11176,7 +10233,7 @@
         <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G25" s="1">
         <v>2018</v>
@@ -11185,10 +10242,10 @@
         <v>43101</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L25" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>137</v>
@@ -11275,575 +10332,575 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A374C9BF-BD00-4473-A5C0-F0EEC750D063}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="E1:Q39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q39"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="29.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="5:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E1" s="27" t="s">
+    <row r="1" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>29</v>
       </c>
+      <c r="B1" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="38"/>
       <c r="F1" s="27" t="s">
-        <v>32</v>
+        <v>495</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="H1" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="38"/>
-      <c r="J1" s="27" t="s">
-        <v>497</v>
-      </c>
-      <c r="K1" s="27" t="s">
-        <v>274</v>
-      </c>
-      <c r="L1" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="M1" s="30"/>
-      <c r="N1" s="29"/>
+        <v>278</v>
+      </c>
+      <c r="I1" s="30"/>
+      <c r="J1" s="29"/>
       <c r="O1" s="29"/>
       <c r="P1" s="29"/>
       <c r="Q1" s="29"/>
     </row>
-    <row r="2" spans="5:17" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="E2" s="34" t="s">
-        <v>486</v>
-      </c>
+    <row r="2" spans="1:17" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="35"/>
       <c r="F2" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="G2" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="H2" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="34" t="s">
-        <v>499</v>
-      </c>
-      <c r="K2" s="36" t="s">
-        <v>498</v>
-      </c>
-      <c r="L2" s="36" t="s">
-        <v>464</v>
-      </c>
-      <c r="M2" s="30"/>
-      <c r="N2" s="29"/>
+        <v>497</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>496</v>
+      </c>
+      <c r="H2" s="36" t="s">
+        <v>462</v>
+      </c>
+      <c r="I2" s="30"/>
+      <c r="J2" s="29"/>
       <c r="O2" s="29"/>
       <c r="P2" s="29"/>
       <c r="Q2" s="29"/>
     </row>
-    <row r="3" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="E3" s="34" t="s">
-        <v>487</v>
-      </c>
-      <c r="F3" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="G3" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H3" s="34" t="s">
+    <row r="3" spans="1:17" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36" t="s">
-        <v>500</v>
-      </c>
-      <c r="K3" s="36" t="s">
-        <v>501</v>
-      </c>
-      <c r="L3" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="M3" s="30"/>
-      <c r="N3" s="29"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36" t="s">
+        <v>498</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>499</v>
+      </c>
+      <c r="H3" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="I3" s="30"/>
+      <c r="J3" s="29"/>
       <c r="O3" s="29"/>
       <c r="P3" s="29"/>
       <c r="Q3" s="29"/>
     </row>
-    <row r="4" spans="5:17" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="E4" s="34" t="s">
-        <v>204</v>
-      </c>
-      <c r="F4" s="34" t="s">
+    <row r="4" spans="1:17" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H4" s="34" t="s">
+      <c r="C4" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I4" s="35"/>
-      <c r="J4" s="36" t="s">
-        <v>502</v>
-      </c>
-      <c r="K4" s="36" t="s">
-        <v>503</v>
-      </c>
-      <c r="L4" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="M4" s="30"/>
-      <c r="N4" s="29"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="36" t="s">
+        <v>500</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>501</v>
+      </c>
+      <c r="H4" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="I4" s="30"/>
+      <c r="J4" s="29"/>
       <c r="O4" s="29"/>
       <c r="P4" s="29"/>
       <c r="Q4" s="29"/>
     </row>
-    <row r="5" spans="5:17" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="E5" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="F5" s="34" t="s">
+    <row r="5" spans="1:17" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H5" s="34" t="s">
+      <c r="C5" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="36" t="s">
-        <v>504</v>
-      </c>
-      <c r="K5" s="36"/>
-      <c r="L5" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="M5" s="30"/>
-      <c r="N5" s="29"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36" t="s">
+        <v>502</v>
+      </c>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="I5" s="30"/>
+      <c r="J5" s="29"/>
       <c r="O5" s="29"/>
       <c r="P5" s="29"/>
       <c r="Q5" s="29"/>
     </row>
-    <row r="6" spans="5:17" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="E6" s="34" t="s">
-        <v>202</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H6" s="34" t="s">
+    <row r="6" spans="1:17" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="36" t="s">
-        <v>506</v>
-      </c>
-      <c r="K6" s="36" t="s">
-        <v>505</v>
-      </c>
-      <c r="L6" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="M6" s="30"/>
-      <c r="N6" s="29"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="36" t="s">
+        <v>504</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="H6" s="36" t="s">
+        <v>288</v>
+      </c>
+      <c r="I6" s="30"/>
+      <c r="J6" s="29"/>
       <c r="O6" s="29"/>
       <c r="P6" s="29"/>
       <c r="Q6" s="29"/>
     </row>
-    <row r="7" spans="5:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E7" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="F7" s="34" t="s">
-        <v>209</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>461</v>
-      </c>
-      <c r="H7" s="34" t="s">
+    <row r="7" spans="1:17" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="36" t="s">
-        <v>507</v>
-      </c>
-      <c r="K7" s="36" t="s">
-        <v>506</v>
-      </c>
-      <c r="L7" s="36" t="s">
-        <v>290</v>
-      </c>
-      <c r="M7" s="30"/>
-      <c r="N7" s="29"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36" t="s">
+        <v>505</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>504</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>289</v>
+      </c>
+      <c r="I7" s="30"/>
+      <c r="J7" s="29"/>
       <c r="O7" s="29"/>
       <c r="P7" s="29"/>
       <c r="Q7" s="29"/>
     </row>
-    <row r="8" spans="5:17" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="E8" s="34" t="s">
-        <v>488</v>
-      </c>
-      <c r="F8" s="34" t="s">
+    <row r="8" spans="1:17" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>486</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="H8" s="34" t="s">
+      <c r="C8" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="K8" s="36" t="s">
+      <c r="E8" s="35"/>
+      <c r="F8" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="L8" s="36" t="s">
-        <v>291</v>
-      </c>
-      <c r="M8" s="30"/>
-      <c r="N8" s="29"/>
+      <c r="G8" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="H8" s="36" t="s">
+        <v>290</v>
+      </c>
+      <c r="I8" s="30"/>
+      <c r="J8" s="29"/>
       <c r="O8" s="29"/>
       <c r="P8" s="29"/>
       <c r="Q8" s="29"/>
     </row>
-    <row r="9" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="E9" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="34" t="s">
+    <row r="9" spans="1:17" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="G9" s="34" t="s">
-        <v>277</v>
-      </c>
-      <c r="H9" s="34" t="s">
+      <c r="C9" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D9" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36" t="s">
-        <v>281</v>
-      </c>
-      <c r="K9" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="L9" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="M9" s="30"/>
-      <c r="N9" s="29"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="36" t="s">
+        <v>280</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>283</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="I9" s="30"/>
+      <c r="J9" s="29"/>
       <c r="O9" s="29"/>
       <c r="P9" s="29"/>
       <c r="Q9" s="29"/>
     </row>
-    <row r="10" spans="5:17" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="E10" s="37" t="s">
-        <v>489</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="H10" s="37" t="s">
+    <row r="10" spans="1:17" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="37" t="s">
+        <v>487</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="D10" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35"/>
-      <c r="L10" s="36" t="s">
-        <v>508</v>
-      </c>
-      <c r="M10" s="30"/>
-      <c r="N10" s="29"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="36" t="s">
+        <v>506</v>
+      </c>
+      <c r="I10" s="30"/>
+      <c r="J10" s="29"/>
       <c r="O10" s="29"/>
       <c r="P10" s="29"/>
       <c r="Q10" s="29"/>
     </row>
-    <row r="11" spans="5:17" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="E11" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="F11" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="G11" s="34" t="s">
-        <v>277</v>
-      </c>
-      <c r="H11" s="34" t="s">
+    <row r="11" spans="1:17" ht="288" x14ac:dyDescent="0.3">
+      <c r="A11" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D11" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="36" t="s">
+      <c r="E11" s="35"/>
+      <c r="F11" s="36" t="s">
+        <v>281</v>
+      </c>
+      <c r="G11" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="K11" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="L11" s="36" t="s">
-        <v>292</v>
-      </c>
-      <c r="M11" s="30"/>
-      <c r="N11" s="29"/>
+      <c r="H11" s="36" t="s">
+        <v>291</v>
+      </c>
+      <c r="I11" s="30"/>
+      <c r="J11" s="29"/>
       <c r="O11" s="29"/>
       <c r="P11" s="29"/>
       <c r="Q11" s="29"/>
     </row>
-    <row r="12" spans="5:17" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="E12" s="34" t="s">
-        <v>490</v>
-      </c>
+    <row r="12" spans="1:17" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="34" t="s">
+        <v>488</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="35"/>
       <c r="F12" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="G12" s="34" t="s">
-        <v>265</v>
-      </c>
-      <c r="H12" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I12" s="35"/>
-      <c r="J12" s="34" t="s">
-        <v>285</v>
-      </c>
-      <c r="K12" s="36" t="s">
-        <v>496</v>
-      </c>
-      <c r="L12" s="36"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="29"/>
+        <v>284</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="H12" s="36"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="29"/>
       <c r="O12" s="29"/>
       <c r="P12" s="29"/>
       <c r="Q12" s="29"/>
     </row>
-    <row r="13" spans="5:17" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="E13" s="34" t="s">
-        <v>200</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>231</v>
-      </c>
-      <c r="H13" s="34" t="s">
+    <row r="13" spans="1:17" ht="216" x14ac:dyDescent="0.3">
+      <c r="A13" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="D13" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="I13" s="35"/>
-      <c r="J13" s="36" t="s">
-        <v>493</v>
-      </c>
-      <c r="K13" s="36" t="s">
-        <v>494</v>
-      </c>
-      <c r="L13" s="36" t="s">
-        <v>493</v>
-      </c>
-      <c r="M13" s="30"/>
-      <c r="N13" s="29"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="36" t="s">
+        <v>491</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>492</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>491</v>
+      </c>
+      <c r="I13" s="30"/>
+      <c r="J13" s="29"/>
       <c r="O13" s="29"/>
       <c r="P13" s="29"/>
       <c r="Q13" s="29"/>
     </row>
-    <row r="14" spans="5:17" ht="216" x14ac:dyDescent="0.3">
-      <c r="E14" s="34" t="s">
-        <v>491</v>
-      </c>
-      <c r="F14" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="G14" s="34" t="s">
-        <v>266</v>
-      </c>
-      <c r="H14" s="34" t="s">
+    <row r="14" spans="1:17" ht="216" x14ac:dyDescent="0.3">
+      <c r="A14" s="34" t="s">
+        <v>489</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="D14" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="K14" s="36" t="s">
-        <v>337</v>
-      </c>
-      <c r="L14" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="M14" s="30"/>
-      <c r="N14" s="29"/>
+      <c r="E14" s="35"/>
+      <c r="F14" s="36" t="s">
+        <v>279</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>336</v>
+      </c>
+      <c r="H14" s="36" t="s">
+        <v>279</v>
+      </c>
+      <c r="I14" s="30"/>
+      <c r="J14" s="29"/>
       <c r="O14" s="29"/>
       <c r="P14" s="29"/>
       <c r="Q14" s="29"/>
     </row>
-    <row r="15" spans="5:17" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="E15" s="34" t="s">
-        <v>492</v>
-      </c>
+    <row r="15" spans="1:17" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="34" t="s">
+        <v>490</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="35"/>
       <c r="F15" s="34" t="s">
-        <v>212</v>
-      </c>
-      <c r="G15" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I15" s="35"/>
-      <c r="J15" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36" t="s">
-        <v>293</v>
-      </c>
-      <c r="M15" s="30"/>
-      <c r="N15" s="29"/>
+        <v>285</v>
+      </c>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36" t="s">
+        <v>292</v>
+      </c>
+      <c r="I15" s="30"/>
+      <c r="J15" s="29"/>
       <c r="O15" s="29"/>
       <c r="P15" s="29"/>
       <c r="Q15" s="29"/>
     </row>
-    <row r="16" spans="5:17" ht="72" x14ac:dyDescent="0.3">
-      <c r="E16" s="34" t="s">
+    <row r="16" spans="1:17" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A16" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="F16" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="G16" s="37" t="s">
-        <v>259</v>
-      </c>
-      <c r="H16" s="34" t="s">
-        <v>273</v>
-      </c>
-      <c r="I16" s="35"/>
-      <c r="J16" s="36" t="s">
+      <c r="B16" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="E16" s="35"/>
+      <c r="F16" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="G16" s="36" t="s">
         <v>287</v>
       </c>
-      <c r="K16" s="36" t="s">
-        <v>288</v>
-      </c>
-      <c r="L16" s="36"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="29"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="29"/>
       <c r="O16" s="29"/>
       <c r="P16" s="29"/>
       <c r="Q16" s="29"/>
     </row>
-    <row r="17" spans="5:17" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="E17" s="34" t="s">
-        <v>207</v>
-      </c>
-      <c r="F17" s="34" t="s">
-        <v>220</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>256</v>
-      </c>
-      <c r="H17" s="34" t="s">
+    <row r="17" spans="1:17" ht="216" x14ac:dyDescent="0.3">
+      <c r="A17" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="D17" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="I17" s="35"/>
-      <c r="J17" s="36" t="s">
-        <v>495</v>
-      </c>
-      <c r="K17" s="36" t="s">
-        <v>495</v>
-      </c>
-      <c r="L17" s="36" t="s">
-        <v>495</v>
-      </c>
-      <c r="M17" s="30"/>
-      <c r="N17" s="29"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="36" t="s">
+        <v>493</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>493</v>
+      </c>
+      <c r="H17" s="36" t="s">
+        <v>493</v>
+      </c>
+      <c r="I17" s="30"/>
+      <c r="J17" s="29"/>
       <c r="O17" s="29"/>
       <c r="P17" s="29"/>
       <c r="Q17" s="29"/>
     </row>
-    <row r="18" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
     </row>
-    <row r="19" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E19" s="1"/>
     </row>
-    <row r="20" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
     </row>
-    <row r="21" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
     </row>
-    <row r="22" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
     </row>
-    <row r="23" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
     </row>
-    <row r="24" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
     </row>
-    <row r="25" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
     </row>
-    <row r="26" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
     </row>
-    <row r="27" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
     </row>
-    <row r="29" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
     </row>
-    <row r="30" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
     </row>
-    <row r="31" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="5:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
@@ -11893,7 +10950,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
